--- a/shared/seguimiento_pueblo.xlsx
+++ b/shared/seguimiento_pueblo.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1096"/>
+  <dimension ref="A1:L1208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -55320,6 +55320,5606 @@
         </is>
       </c>
     </row>
+    <row r="1097">
+      <c r="A1097" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B1097" s="5" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="C1097" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1097" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1097" s="6" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="F1097" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1097" s="8" t="n"/>
+      <c r="H1097" s="8" t="n"/>
+      <c r="I1097" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1097" s="9" t="inlineStr">
+        <is>
+          <t>sembrar_seguimiento_pueblo</t>
+        </is>
+      </c>
+      <c r="K1097" s="10" t="inlineStr">
+        <is>
+          <t>siembra_2026-06_CONVENIO_F_3A</t>
+        </is>
+      </c>
+      <c r="L1097" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B1098" s="5" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C1098" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1098" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1098" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1098" s="8" t="n"/>
+      <c r="G1098" s="8" t="n"/>
+      <c r="H1098" s="7" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I1098" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1098" s="9" t="inlineStr">
+        <is>
+          <t>correccion_manual</t>
+        </is>
+      </c>
+      <c r="K1098" s="10" t="inlineStr">
+        <is>
+          <t>correccion_lote_F3B_a_F3A_20260704</t>
+        </is>
+      </c>
+      <c r="L1098" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:31:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B1099" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1099" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1099" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1099" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1099" s="8" t="n"/>
+      <c r="G1099" s="8" t="n"/>
+      <c r="H1099" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1099" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1099" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1099" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_A_1</t>
+        </is>
+      </c>
+      <c r="L1099" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B1100" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1100" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1100" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1100" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1100" s="8" t="n"/>
+      <c r="G1100" s="8" t="n"/>
+      <c r="H1100" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1100" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1100" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_A_5</t>
+        </is>
+      </c>
+      <c r="L1100" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B1101" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C1101" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1101" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1101" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1101" s="8" t="n"/>
+      <c r="G1101" s="8" t="n"/>
+      <c r="H1101" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1101" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1101" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1101" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_A_6</t>
+        </is>
+      </c>
+      <c r="L1101" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B1102" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1102" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1102" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1102" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1102" s="8" t="n"/>
+      <c r="G1102" s="8" t="n"/>
+      <c r="H1102" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1102" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1102" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1102" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_A_8</t>
+        </is>
+      </c>
+      <c r="L1102" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B1103" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C1103" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1103" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1103" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1103" s="8" t="n"/>
+      <c r="G1103" s="8" t="n"/>
+      <c r="H1103" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1103" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1103" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_B_2</t>
+        </is>
+      </c>
+      <c r="L1103" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B1104" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C1104" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1104" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1104" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1104" s="8" t="n"/>
+      <c r="G1104" s="8" t="n"/>
+      <c r="H1104" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1104" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1104" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1104" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_B_6</t>
+        </is>
+      </c>
+      <c r="L1104" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B1105" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1105" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1105" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1105" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1105" s="8" t="n"/>
+      <c r="G1105" s="8" t="n"/>
+      <c r="H1105" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1105" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1105" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1105" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_B_8</t>
+        </is>
+      </c>
+      <c r="L1105" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1106" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C1106" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1106" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1106" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1106" s="8" t="n"/>
+      <c r="G1106" s="8" t="n"/>
+      <c r="H1106" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1106" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1106" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_13</t>
+        </is>
+      </c>
+      <c r="L1106" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1107" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C1107" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1107" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1107" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1107" s="8" t="n"/>
+      <c r="G1107" s="8" t="n"/>
+      <c r="H1107" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1107" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1107" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_18</t>
+        </is>
+      </c>
+      <c r="L1107" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1108" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C1108" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1108" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1108" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1108" s="8" t="n"/>
+      <c r="G1108" s="8" t="n"/>
+      <c r="H1108" s="7" t="n">
+        <v>-47</v>
+      </c>
+      <c r="I1108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1108" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1108" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_19</t>
+        </is>
+      </c>
+      <c r="L1108" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1109" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C1109" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1109" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1109" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1109" s="8" t="n"/>
+      <c r="G1109" s="8" t="n"/>
+      <c r="H1109" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1109" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1109" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_2</t>
+        </is>
+      </c>
+      <c r="L1109" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1110" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C1110" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1110" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1110" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1110" s="8" t="n"/>
+      <c r="G1110" s="8" t="n"/>
+      <c r="H1110" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1110" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J1110" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1110" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_20</t>
+        </is>
+      </c>
+      <c r="L1110" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1111" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C1111" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1111" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1111" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1111" s="8" t="n"/>
+      <c r="G1111" s="8" t="n"/>
+      <c r="H1111" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I1111" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J1111" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1111" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_25</t>
+        </is>
+      </c>
+      <c r="L1111" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1112" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C1112" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1112" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1112" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1112" s="8" t="n"/>
+      <c r="G1112" s="8" t="n"/>
+      <c r="H1112" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1112" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1112" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1112" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_32</t>
+        </is>
+      </c>
+      <c r="L1112" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1113" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C1113" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1113" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1113" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1113" s="8" t="n"/>
+      <c r="G1113" s="8" t="n"/>
+      <c r="H1113" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1113" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1113" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_4</t>
+        </is>
+      </c>
+      <c r="L1113" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1114" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1114" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1114" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1114" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1114" s="8" t="n"/>
+      <c r="G1114" s="8" t="n"/>
+      <c r="H1114" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1114" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1114" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1114" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_5</t>
+        </is>
+      </c>
+      <c r="L1114" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1115" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C1115" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1115" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1115" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1115" s="8" t="n"/>
+      <c r="G1115" s="8" t="n"/>
+      <c r="H1115" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1115" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1115" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1115" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_C_7</t>
+        </is>
+      </c>
+      <c r="L1115" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B1116" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1116" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1116" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1116" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1116" s="8" t="n"/>
+      <c r="G1116" s="8" t="n"/>
+      <c r="H1116" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1116" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1116" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1116" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_D_1</t>
+        </is>
+      </c>
+      <c r="L1116" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B1117" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C1117" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1117" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1117" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1117" s="8" t="n"/>
+      <c r="G1117" s="8" t="n"/>
+      <c r="H1117" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1117" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1117" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1117" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_D_19</t>
+        </is>
+      </c>
+      <c r="L1117" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B1118" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C1118" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1118" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1118" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1118" s="8" t="n"/>
+      <c r="G1118" s="8" t="n"/>
+      <c r="H1118" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1118" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1118" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1118" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_D_3</t>
+        </is>
+      </c>
+      <c r="L1118" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B1119" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C1119" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1119" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1119" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1119" s="8" t="n"/>
+      <c r="G1119" s="8" t="n"/>
+      <c r="H1119" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1119" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1119" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1119" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_D_6</t>
+        </is>
+      </c>
+      <c r="L1119" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B1120" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1120" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1120" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1120" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1120" s="8" t="n"/>
+      <c r="G1120" s="8" t="n"/>
+      <c r="H1120" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1120" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1120" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1120" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_D_8</t>
+        </is>
+      </c>
+      <c r="L1120" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1121" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1121" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1121" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1121" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1121" s="8" t="n"/>
+      <c r="G1121" s="8" t="n"/>
+      <c r="H1121" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1121" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="J1121" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1121" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_E_12</t>
+        </is>
+      </c>
+      <c r="L1121" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1122" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C1122" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1122" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1122" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1122" s="8" t="n"/>
+      <c r="G1122" s="8" t="n"/>
+      <c r="H1122" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1122" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1122" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1122" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_E_2</t>
+        </is>
+      </c>
+      <c r="L1122" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1123" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1123" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1123" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1123" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1123" s="8" t="n"/>
+      <c r="G1123" s="8" t="n"/>
+      <c r="H1123" s="7" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I1123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1123" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1123" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_E_9</t>
+        </is>
+      </c>
+      <c r="L1123" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="5" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B1124" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1124" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1124" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1124" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1124" s="8" t="n"/>
+      <c r="G1124" s="8" t="n"/>
+      <c r="H1124" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1124" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1124" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_F1_8</t>
+        </is>
+      </c>
+      <c r="L1124" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B1125" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1125" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1125" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1125" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1125" s="8" t="n"/>
+      <c r="G1125" s="8" t="n"/>
+      <c r="H1125" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1125" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1125" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1125" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_F_12</t>
+        </is>
+      </c>
+      <c r="L1125" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B1126" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C1126" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1126" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1126" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1126" s="8" t="n"/>
+      <c r="G1126" s="8" t="n"/>
+      <c r="H1126" s="7" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I1126" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1126" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1126" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_F_14</t>
+        </is>
+      </c>
+      <c r="L1126" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B1127" s="5" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="C1127" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1127" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1127" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1127" s="8" t="n"/>
+      <c r="G1127" s="8" t="n"/>
+      <c r="H1127" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1127" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1127" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1127" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_F_3A</t>
+        </is>
+      </c>
+      <c r="L1127" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B1128" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C1128" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1128" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1128" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1128" s="8" t="n"/>
+      <c r="G1128" s="8" t="n"/>
+      <c r="H1128" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1128" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1128" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1128" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_F_7</t>
+        </is>
+      </c>
+      <c r="L1128" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B1129" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1129" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1129" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1129" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1129" s="8" t="n"/>
+      <c r="G1129" s="8" t="n"/>
+      <c r="H1129" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1129" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1129" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_F_8</t>
+        </is>
+      </c>
+      <c r="L1129" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B1130" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1130" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1130" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1130" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1130" s="8" t="n"/>
+      <c r="G1130" s="8" t="n"/>
+      <c r="H1130" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1130" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1130" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1130" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_F_9</t>
+        </is>
+      </c>
+      <c r="L1130" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B1131" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1131" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1131" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1131" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1131" s="8" t="n"/>
+      <c r="G1131" s="8" t="n"/>
+      <c r="H1131" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1131" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1131" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1131" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_G1_5</t>
+        </is>
+      </c>
+      <c r="L1131" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1132" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C1132" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1132" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1132" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1132" s="8" t="n"/>
+      <c r="G1132" s="8" t="n"/>
+      <c r="H1132" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1132" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1132" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1132" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_G_11</t>
+        </is>
+      </c>
+      <c r="L1132" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1133" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1133" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1133" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1133" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1133" s="8" t="n"/>
+      <c r="G1133" s="8" t="n"/>
+      <c r="H1133" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1133" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1133" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1133" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_G_12</t>
+        </is>
+      </c>
+      <c r="L1133" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1134" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C1134" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1134" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1134" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1134" s="8" t="n"/>
+      <c r="G1134" s="8" t="n"/>
+      <c r="H1134" s="7" t="n">
+        <v>-26</v>
+      </c>
+      <c r="I1134" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="J1134" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1134" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_G_14</t>
+        </is>
+      </c>
+      <c r="L1134" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1135" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C1135" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1135" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1135" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1135" s="8" t="n"/>
+      <c r="G1135" s="8" t="n"/>
+      <c r="H1135" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1135" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1135" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1135" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_G_17</t>
+        </is>
+      </c>
+      <c r="L1135" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1136" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C1136" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1136" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1136" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1136" s="8" t="n"/>
+      <c r="G1136" s="8" t="n"/>
+      <c r="H1136" s="7" t="n">
+        <v>-75</v>
+      </c>
+      <c r="I1136" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1136" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1136" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_G_19</t>
+        </is>
+      </c>
+      <c r="L1136" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1137" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C1137" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1137" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1137" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1137" s="8" t="n"/>
+      <c r="G1137" s="8" t="n"/>
+      <c r="H1137" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1137" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1137" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_G_2</t>
+        </is>
+      </c>
+      <c r="L1137" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1138" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C1138" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1138" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1138" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1138" s="8" t="n"/>
+      <c r="G1138" s="8" t="n"/>
+      <c r="H1138" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1138" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1138" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1138" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_G_20</t>
+        </is>
+      </c>
+      <c r="L1138" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1139" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C1139" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1139" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1139" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1139" s="8" t="n"/>
+      <c r="G1139" s="8" t="n"/>
+      <c r="H1139" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1139" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1139" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_G_3</t>
+        </is>
+      </c>
+      <c r="L1139" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1140" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1140" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1140" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1140" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1140" s="8" t="n"/>
+      <c r="G1140" s="8" t="n"/>
+      <c r="H1140" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1140" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="J1140" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1140" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_H_1</t>
+        </is>
+      </c>
+      <c r="L1140" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1141" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C1141" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1141" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1141" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1141" s="8" t="n"/>
+      <c r="G1141" s="8" t="n"/>
+      <c r="H1141" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1141" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1141" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1141" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_H_11</t>
+        </is>
+      </c>
+      <c r="L1141" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:08:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1142" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1142" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1142" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1142" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1142" s="8" t="n"/>
+      <c r="G1142" s="8" t="n"/>
+      <c r="H1142" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1142" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1142" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1142" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_H_12</t>
+        </is>
+      </c>
+      <c r="L1142" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1143" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C1143" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1143" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1143" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1143" s="8" t="n"/>
+      <c r="G1143" s="8" t="n"/>
+      <c r="H1143" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1143" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1143" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1143" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_H_18</t>
+        </is>
+      </c>
+      <c r="L1143" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1144" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C1144" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1144" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1144" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1144" s="8" t="n"/>
+      <c r="G1144" s="8" t="n"/>
+      <c r="H1144" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1144" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1144" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1144" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_H_19</t>
+        </is>
+      </c>
+      <c r="L1144" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1145" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1145" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1145" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1145" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1145" s="8" t="n"/>
+      <c r="G1145" s="8" t="n"/>
+      <c r="H1145" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1145" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1145" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1145" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_H_5</t>
+        </is>
+      </c>
+      <c r="L1145" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1146" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1146" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1146" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1146" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1146" s="8" t="n"/>
+      <c r="G1146" s="8" t="n"/>
+      <c r="H1146" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1146" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1146" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1146" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_H_8</t>
+        </is>
+      </c>
+      <c r="L1146" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1147" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1147" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1147" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1147" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1147" s="8" t="n"/>
+      <c r="G1147" s="8" t="n"/>
+      <c r="H1147" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1147" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1147" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1147" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_H_9</t>
+        </is>
+      </c>
+      <c r="L1147" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1148" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1148" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1148" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1148" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1148" s="8" t="n"/>
+      <c r="G1148" s="8" t="n"/>
+      <c r="H1148" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1148" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1148" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1148" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_I_1</t>
+        </is>
+      </c>
+      <c r="L1148" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1149" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C1149" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1149" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1149" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1149" s="8" t="n"/>
+      <c r="G1149" s="8" t="n"/>
+      <c r="H1149" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1149" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1149" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1149" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_I_11</t>
+        </is>
+      </c>
+      <c r="L1149" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1150" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1150" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1150" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1150" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1150" s="8" t="n"/>
+      <c r="G1150" s="8" t="n"/>
+      <c r="H1150" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1150" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1150" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1150" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_I_12</t>
+        </is>
+      </c>
+      <c r="L1150" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1151" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C1151" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1151" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1151" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1151" s="8" t="n"/>
+      <c r="G1151" s="8" t="n"/>
+      <c r="H1151" s="7" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I1151" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1151" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1151" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_I_13</t>
+        </is>
+      </c>
+      <c r="L1151" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1152" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C1152" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1152" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1152" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1152" s="8" t="n"/>
+      <c r="G1152" s="8" t="n"/>
+      <c r="H1152" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1152" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1152" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1152" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_I_14</t>
+        </is>
+      </c>
+      <c r="L1152" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1153" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C1153" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1153" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1153" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1153" s="8" t="n"/>
+      <c r="G1153" s="8" t="n"/>
+      <c r="H1153" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1153" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1153" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1153" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_I_15</t>
+        </is>
+      </c>
+      <c r="L1153" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1154" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C1154" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1154" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1154" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1154" s="8" t="n"/>
+      <c r="G1154" s="8" t="n"/>
+      <c r="H1154" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1154" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1154" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1154" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_I_17</t>
+        </is>
+      </c>
+      <c r="L1154" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B1155" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C1155" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1155" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1155" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1155" s="8" t="n"/>
+      <c r="G1155" s="8" t="n"/>
+      <c r="H1155" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1155" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1155" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1155" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_J_4</t>
+        </is>
+      </c>
+      <c r="L1155" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B1156" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1156" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1156" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1156" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1156" s="8" t="n"/>
+      <c r="G1156" s="8" t="n"/>
+      <c r="H1156" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1156" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1156" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1156" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_J_5</t>
+        </is>
+      </c>
+      <c r="L1156" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B1157" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C1157" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1157" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1157" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1157" s="8" t="n"/>
+      <c r="G1157" s="8" t="n"/>
+      <c r="H1157" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1157" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1157" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1157" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_J_7</t>
+        </is>
+      </c>
+      <c r="L1157" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B1158" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1158" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1158" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1158" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1158" s="8" t="n"/>
+      <c r="G1158" s="8" t="n"/>
+      <c r="H1158" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1158" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1158" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1158" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_J_8</t>
+        </is>
+      </c>
+      <c r="L1158" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B1159" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1159" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1159" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1159" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1159" s="8" t="n"/>
+      <c r="G1159" s="8" t="n"/>
+      <c r="H1159" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1159" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1159" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1159" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_J_9</t>
+        </is>
+      </c>
+      <c r="L1159" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B1160" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1160" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1160" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1160" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1160" s="8" t="n"/>
+      <c r="G1160" s="8" t="n"/>
+      <c r="H1160" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1160" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1160" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1160" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_K_1</t>
+        </is>
+      </c>
+      <c r="L1160" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B1161" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C1161" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1161" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1161" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1161" s="8" t="n"/>
+      <c r="G1161" s="8" t="n"/>
+      <c r="H1161" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1161" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1161" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1161" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_K_17</t>
+        </is>
+      </c>
+      <c r="L1161" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B1162" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C1162" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1162" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1162" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1162" s="8" t="n"/>
+      <c r="G1162" s="8" t="n"/>
+      <c r="H1162" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1162" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1162" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1162" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_K_2</t>
+        </is>
+      </c>
+      <c r="L1162" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B1163" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C1163" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1163" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1163" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1163" s="8" t="n"/>
+      <c r="G1163" s="8" t="n"/>
+      <c r="H1163" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1163" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1163" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1163" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_K_4</t>
+        </is>
+      </c>
+      <c r="L1163" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B1164" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C1164" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1164" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1164" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1164" s="8" t="n"/>
+      <c r="G1164" s="8" t="n"/>
+      <c r="H1164" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1164" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1164" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1164" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_K_6</t>
+        </is>
+      </c>
+      <c r="L1164" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B1165" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1165" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1165" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1165" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1165" s="8" t="n"/>
+      <c r="G1165" s="8" t="n"/>
+      <c r="H1165" s="7" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I1165" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1165" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1165" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_K_8</t>
+        </is>
+      </c>
+      <c r="L1165" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1166" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1166" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1166" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1166" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1166" s="8" t="n"/>
+      <c r="G1166" s="8" t="n"/>
+      <c r="H1166" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1166" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1166" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1166" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_1</t>
+        </is>
+      </c>
+      <c r="L1166" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1167" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C1167" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1167" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1167" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1167" s="8" t="n"/>
+      <c r="G1167" s="8" t="n"/>
+      <c r="H1167" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1167" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1167" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1167" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_10</t>
+        </is>
+      </c>
+      <c r="L1167" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1168" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C1168" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1168" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1168" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1168" s="8" t="n"/>
+      <c r="G1168" s="8" t="n"/>
+      <c r="H1168" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1168" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1168" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1168" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_11</t>
+        </is>
+      </c>
+      <c r="L1168" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1169" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1169" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1169" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1169" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1169" s="8" t="n"/>
+      <c r="G1169" s="8" t="n"/>
+      <c r="H1169" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1169" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1169" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1169" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_12</t>
+        </is>
+      </c>
+      <c r="L1169" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1170" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C1170" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1170" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1170" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1170" s="8" t="n"/>
+      <c r="G1170" s="8" t="n"/>
+      <c r="H1170" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1170" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1170" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1170" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_14</t>
+        </is>
+      </c>
+      <c r="L1170" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1171" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C1171" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1171" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1171" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1171" s="8" t="n"/>
+      <c r="G1171" s="8" t="n"/>
+      <c r="H1171" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1171" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1171" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1171" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_2</t>
+        </is>
+      </c>
+      <c r="L1171" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1172" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C1172" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1172" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1172" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1172" s="8" t="n"/>
+      <c r="G1172" s="8" t="n"/>
+      <c r="H1172" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1172" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1172" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1172" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_3</t>
+        </is>
+      </c>
+      <c r="L1172" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1173" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C1173" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1173" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1173" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1173" s="8" t="n"/>
+      <c r="G1173" s="8" t="n"/>
+      <c r="H1173" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1173" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1173" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1173" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_4</t>
+        </is>
+      </c>
+      <c r="L1173" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1174" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C1174" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1174" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1174" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1174" s="8" t="n"/>
+      <c r="G1174" s="8" t="n"/>
+      <c r="H1174" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1174" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1174" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1174" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_6</t>
+        </is>
+      </c>
+      <c r="L1174" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1175" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C1175" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1175" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1175" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1175" s="8" t="n"/>
+      <c r="G1175" s="8" t="n"/>
+      <c r="H1175" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1175" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1175" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1175" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_7</t>
+        </is>
+      </c>
+      <c r="L1175" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1176" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1176" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1176" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1176" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1176" s="8" t="n"/>
+      <c r="G1176" s="8" t="n"/>
+      <c r="H1176" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1176" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1176" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1176" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_L_8</t>
+        </is>
+      </c>
+      <c r="L1176" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1177" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C1177" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1177" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1177" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1177" s="8" t="n"/>
+      <c r="G1177" s="8" t="n"/>
+      <c r="H1177" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1177" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1177" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1177" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_M_14</t>
+        </is>
+      </c>
+      <c r="L1177" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1178" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C1178" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1178" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1178" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1178" s="8" t="n"/>
+      <c r="G1178" s="8" t="n"/>
+      <c r="H1178" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1178" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1178" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1178" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_M_19</t>
+        </is>
+      </c>
+      <c r="L1178" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1179" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C1179" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1179" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1179" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1179" s="8" t="n"/>
+      <c r="G1179" s="8" t="n"/>
+      <c r="H1179" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1179" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1179" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1179" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_M_22</t>
+        </is>
+      </c>
+      <c r="L1179" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1180" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1180" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1180" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1180" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1180" s="8" t="n"/>
+      <c r="G1180" s="8" t="n"/>
+      <c r="H1180" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1180" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1180" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1180" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_M_9</t>
+        </is>
+      </c>
+      <c r="L1180" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B1181" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1181" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1181" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1181" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1181" s="8" t="n"/>
+      <c r="G1181" s="8" t="n"/>
+      <c r="H1181" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1181" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1181" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1181" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_N_1</t>
+        </is>
+      </c>
+      <c r="L1181" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B1182" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C1182" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1182" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1182" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1182" s="8" t="n"/>
+      <c r="G1182" s="8" t="n"/>
+      <c r="H1182" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1182" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1182" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1182" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_N_2</t>
+        </is>
+      </c>
+      <c r="L1182" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B1183" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C1183" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1183" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1183" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1183" s="8" t="n"/>
+      <c r="G1183" s="8" t="n"/>
+      <c r="H1183" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1183" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="J1183" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1183" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_N_3</t>
+        </is>
+      </c>
+      <c r="L1183" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1184" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1184" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1184" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1184" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1184" s="8" t="n"/>
+      <c r="G1184" s="8" t="n"/>
+      <c r="H1184" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1184" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1184" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1184" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_1</t>
+        </is>
+      </c>
+      <c r="L1184" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1185" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1185" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1185" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1185" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1185" s="8" t="n"/>
+      <c r="G1185" s="8" t="n"/>
+      <c r="H1185" s="7" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I1185" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1185" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1185" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_12</t>
+        </is>
+      </c>
+      <c r="L1185" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1186" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C1186" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1186" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1186" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1186" s="8" t="n"/>
+      <c r="G1186" s="8" t="n"/>
+      <c r="H1186" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1186" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1186" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1186" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_17</t>
+        </is>
+      </c>
+      <c r="L1186" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1187" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C1187" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1187" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1187" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1187" s="8" t="n"/>
+      <c r="G1187" s="8" t="n"/>
+      <c r="H1187" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1187" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1187" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1187" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_19</t>
+        </is>
+      </c>
+      <c r="L1187" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1188" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C1188" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1188" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1188" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1188" s="8" t="n"/>
+      <c r="G1188" s="8" t="n"/>
+      <c r="H1188" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1188" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1188" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1188" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_22</t>
+        </is>
+      </c>
+      <c r="L1188" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1189" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C1189" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1189" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1189" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1189" s="8" t="n"/>
+      <c r="G1189" s="8" t="n"/>
+      <c r="H1189" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1189" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1189" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1189" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_25</t>
+        </is>
+      </c>
+      <c r="L1189" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1190" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C1190" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1190" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1190" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1190" s="8" t="n"/>
+      <c r="G1190" s="8" t="n"/>
+      <c r="H1190" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1190" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1190" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1190" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_26</t>
+        </is>
+      </c>
+      <c r="L1190" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1191" s="5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C1191" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1191" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1191" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1191" s="8" t="n"/>
+      <c r="G1191" s="8" t="n"/>
+      <c r="H1191" s="7" t="n">
+        <v>-75</v>
+      </c>
+      <c r="I1191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1191" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1191" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_28</t>
+        </is>
+      </c>
+      <c r="L1191" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1192" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C1192" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1192" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1192" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1192" s="8" t="n"/>
+      <c r="G1192" s="8" t="n"/>
+      <c r="H1192" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1192" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1192" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1192" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_4</t>
+        </is>
+      </c>
+      <c r="L1192" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1193" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C1193" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1193" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1193" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1193" s="8" t="n"/>
+      <c r="G1193" s="8" t="n"/>
+      <c r="H1193" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1193" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1193" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1193" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_6</t>
+        </is>
+      </c>
+      <c r="L1193" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1194" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1194" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1194" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1194" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1194" s="8" t="n"/>
+      <c r="G1194" s="8" t="n"/>
+      <c r="H1194" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1194" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1194" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1194" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_8</t>
+        </is>
+      </c>
+      <c r="L1194" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1195" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1195" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1195" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1195" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1195" s="8" t="n"/>
+      <c r="G1195" s="8" t="n"/>
+      <c r="H1195" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1195" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1195" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_O_9</t>
+        </is>
+      </c>
+      <c r="L1195" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B1196" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1196" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1196" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1196" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1196" s="8" t="n"/>
+      <c r="G1196" s="8" t="n"/>
+      <c r="H1196" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1196" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1196" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1196" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_P_12</t>
+        </is>
+      </c>
+      <c r="L1196" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B1197" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C1197" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1197" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1197" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1197" s="8" t="n"/>
+      <c r="G1197" s="8" t="n"/>
+      <c r="H1197" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1197" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1197" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_P_13</t>
+        </is>
+      </c>
+      <c r="L1197" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B1198" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C1198" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1198" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1198" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1198" s="8" t="n"/>
+      <c r="G1198" s="8" t="n"/>
+      <c r="H1198" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1198" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1198" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1198" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_P_3</t>
+        </is>
+      </c>
+      <c r="L1198" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="5" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B1199" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1199" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1199" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1199" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1199" s="8" t="n"/>
+      <c r="G1199" s="8" t="n"/>
+      <c r="H1199" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1199" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1199" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1199" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_Q_5</t>
+        </is>
+      </c>
+      <c r="L1199" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="5" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B1200" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1200" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1200" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1200" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1200" s="8" t="n"/>
+      <c r="G1200" s="8" t="n"/>
+      <c r="H1200" s="7" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I1200" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J1200" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1200" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_Q_8</t>
+        </is>
+      </c>
+      <c r="L1200" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B1201" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C1201" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1201" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1201" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1201" s="8" t="n"/>
+      <c r="G1201" s="8" t="n"/>
+      <c r="H1201" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1201" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1201" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1201" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_R_2</t>
+        </is>
+      </c>
+      <c r="L1201" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B1202" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C1202" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1202" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1202" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1202" s="8" t="n"/>
+      <c r="G1202" s="8" t="n"/>
+      <c r="H1202" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1202" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1202" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1202" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_S_3</t>
+        </is>
+      </c>
+      <c r="L1202" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B1203" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C1203" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1203" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1203" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1203" s="8" t="n"/>
+      <c r="G1203" s="8" t="n"/>
+      <c r="H1203" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1203" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1203" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1203" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_S_4</t>
+        </is>
+      </c>
+      <c r="L1203" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B1204" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1204" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1204" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1204" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1204" s="8" t="n"/>
+      <c r="G1204" s="8" t="n"/>
+      <c r="H1204" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1204" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1204" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1204" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_T_8</t>
+        </is>
+      </c>
+      <c r="L1204" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1205" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C1205" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1205" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1205" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1205" s="8" t="n"/>
+      <c r="G1205" s="8" t="n"/>
+      <c r="H1205" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I1205" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="J1205" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1205" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_W_3</t>
+        </is>
+      </c>
+      <c r="L1205" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1206" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C1206" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1206" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1206" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1206" s="8" t="n"/>
+      <c r="G1206" s="8" t="n"/>
+      <c r="H1206" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I1206" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1206" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1206" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_W_4</t>
+        </is>
+      </c>
+      <c r="L1206" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1207" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1207" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1207" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1207" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1207" s="8" t="n"/>
+      <c r="G1207" s="8" t="n"/>
+      <c r="H1207" s="7" t="n">
+        <v>-72</v>
+      </c>
+      <c r="I1207" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1207" s="9" t="inlineStr">
+        <is>
+          <t>correccion_genesis_formula</t>
+        </is>
+      </c>
+      <c r="K1207" s="10" t="inlineStr">
+        <is>
+          <t>correccion_formula_abril_W_5</t>
+        </is>
+      </c>
+      <c r="L1207" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="5" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="B1208" s="5" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C1208" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1208" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1208" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1208" s="8" t="n"/>
+      <c r="G1208" s="8" t="n"/>
+      <c r="H1208" s="7" t="n">
+        <v>-1334</v>
+      </c>
+      <c r="I1208" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1208" s="9" t="inlineStr">
+        <is>
+          <t>correccion_manual</t>
+        </is>
+      </c>
+      <c r="K1208" s="10" t="inlineStr">
+        <is>
+          <t>anulacion_fila_totales_genesis_20260704</t>
+        </is>
+      </c>
+      <c r="L1208" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04 11:16:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="C1:E1"/>

--- a/shared/seguimiento_pueblo.xlsx
+++ b/shared/seguimiento_pueblo.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1488"/>
+  <dimension ref="A1:N1565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -79585,12 +79585,12 @@
     <row r="1427">
       <c r="A1427" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B1427" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1427" s="6" t="inlineStr">
@@ -79623,12 +79623,12 @@
       </c>
       <c r="K1427" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|C-21-MULTA</t>
+          <t>notas_2026-07|Q-4-MULTA-condonacion-unificacion-Q5</t>
         </is>
       </c>
       <c r="L1427" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 10:52:53</t>
+          <t>2026-07-30 11:19:20</t>
         </is>
       </c>
       <c r="M1427" s="9" t="inlineStr">
@@ -79645,17 +79645,17 @@
     <row r="1428">
       <c r="A1428" s="5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B1428" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1428" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1428" s="6" t="inlineStr">
@@ -79670,7 +79670,7 @@
       </c>
       <c r="F1428" s="8" t="n"/>
       <c r="G1428" s="7" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H1428" s="8" t="n"/>
       <c r="I1428" s="7" t="n">
@@ -79683,12 +79683,12 @@
       </c>
       <c r="K1428" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|J-6-MULTA</t>
+          <t>notas_2026-07|Q-4-ACUERDOS-condonacion-unificacion-Q5</t>
         </is>
       </c>
       <c r="L1428" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 10:52:54</t>
+          <t>2026-07-30 11:19:21</t>
         </is>
       </c>
       <c r="M1428" s="9" t="inlineStr">
@@ -79705,17 +79705,17 @@
     <row r="1429">
       <c r="A1429" s="5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B1429" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C1429" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1429" s="6" t="inlineStr">
@@ -79725,182 +79725,167 @@
       </c>
       <c r="E1429" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
-        </is>
-      </c>
-      <c r="F1429" s="8" t="n"/>
-      <c r="G1429" s="7" t="n">
-        <v>75</v>
-      </c>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="F1429" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1429" s="8" t="n"/>
       <c r="H1429" s="8" t="n"/>
       <c r="I1429" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J1429" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>genesis_tardia</t>
         </is>
       </c>
       <c r="K1429" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|J-6-ACUERDOS</t>
+          <t>genesis_tardia_2026-07_MULTA_M_12</t>
         </is>
       </c>
       <c r="L1429" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 10:52:55</t>
+          <t>2026-07-30 11:47:37</t>
         </is>
       </c>
       <c r="M1429" s="9" t="inlineStr">
         <is>
-          <t>DECLARACION_SECRETARIA</t>
-        </is>
-      </c>
-      <c r="N1429" t="inlineStr">
-        <is>
-          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
+          <t>GENESIS</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" s="5" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B1430" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C1430" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1430" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E1430" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
-        </is>
-      </c>
-      <c r="F1430" s="8" t="n"/>
-      <c r="G1430" s="7" t="n">
-        <v>50</v>
-      </c>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="F1430" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1430" s="8" t="n"/>
       <c r="H1430" s="8" t="n"/>
       <c r="I1430" s="7" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J1430" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>genesis_tardia</t>
         </is>
       </c>
       <c r="K1430" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|Q-4-MULTA-condonacion-unificacion-Q5</t>
+          <t>genesis_tardia_2026-07_CONVENIO_P_6</t>
         </is>
       </c>
       <c r="L1430" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:19:20</t>
+          <t>2026-07-30 11:47:38</t>
         </is>
       </c>
       <c r="M1430" s="9" t="inlineStr">
         <is>
-          <t>DECLARACION_SECRETARIA</t>
-        </is>
-      </c>
-      <c r="N1430" t="inlineStr">
-        <is>
-          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
+          <t>GENESIS</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" s="5" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B1431" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C1431" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1431" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E1431" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
-        </is>
-      </c>
-      <c r="F1431" s="8" t="n"/>
-      <c r="G1431" s="7" t="n">
-        <v>75</v>
-      </c>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="F1431" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G1431" s="8" t="n"/>
       <c r="H1431" s="8" t="n"/>
       <c r="I1431" s="7" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J1431" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>genesis_tardia</t>
         </is>
       </c>
       <c r="K1431" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|Q-4-ACUERDOS-condonacion-unificacion-Q5</t>
+          <t>genesis_tardia_2026-07_CONVENIO_H1_2</t>
         </is>
       </c>
       <c r="L1431" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:19:21</t>
+          <t>2026-07-30 11:47:39</t>
         </is>
       </c>
       <c r="M1431" s="9" t="inlineStr">
         <is>
-          <t>DECLARACION_SECRETARIA</t>
-        </is>
-      </c>
-      <c r="N1431" t="inlineStr">
-        <is>
-          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
+          <t>GENESIS</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" s="5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B1432" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C1432" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1432" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E1432" s="6" t="inlineStr">
@@ -79909,12 +79894,12 @@
         </is>
       </c>
       <c r="F1432" s="7" t="n">
-        <v>30</v>
+        <v>263</v>
       </c>
       <c r="G1432" s="8" t="n"/>
       <c r="H1432" s="8" t="n"/>
       <c r="I1432" s="7" t="n">
-        <v>30</v>
+        <v>263</v>
       </c>
       <c r="J1432" s="9" t="inlineStr">
         <is>
@@ -79923,12 +79908,12 @@
       </c>
       <c r="K1432" s="10" t="inlineStr">
         <is>
-          <t>genesis_tardia_2026-07_MULTA_M_12</t>
+          <t>genesis_tardia_2026-07_CONVENIO_B_20</t>
         </is>
       </c>
       <c r="L1432" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:37</t>
+          <t>2026-07-30 11:47:40</t>
         </is>
       </c>
       <c r="M1432" s="9" t="inlineStr">
@@ -79940,12 +79925,12 @@
     <row r="1433">
       <c r="A1433" s="5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B1433" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C1433" s="6" t="inlineStr">
@@ -79964,12 +79949,12 @@
         </is>
       </c>
       <c r="F1433" s="7" t="n">
-        <v>58</v>
+        <v>334</v>
       </c>
       <c r="G1433" s="8" t="n"/>
       <c r="H1433" s="8" t="n"/>
       <c r="I1433" s="7" t="n">
-        <v>58</v>
+        <v>334</v>
       </c>
       <c r="J1433" s="9" t="inlineStr">
         <is>
@@ -79978,12 +79963,12 @@
       </c>
       <c r="K1433" s="10" t="inlineStr">
         <is>
-          <t>genesis_tardia_2026-07_CONVENIO_P_6</t>
+          <t>genesis_tardia_2026-07_CONVENIO_C_43</t>
         </is>
       </c>
       <c r="L1433" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:38</t>
+          <t>2026-07-30 11:47:41</t>
         </is>
       </c>
       <c r="M1433" s="9" t="inlineStr">
@@ -79995,12 +79980,12 @@
     <row r="1434">
       <c r="A1434" s="5" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B1434" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C1434" s="6" t="inlineStr">
@@ -80019,12 +80004,12 @@
         </is>
       </c>
       <c r="F1434" s="7" t="n">
-        <v>1100</v>
+        <v>94</v>
       </c>
       <c r="G1434" s="8" t="n"/>
       <c r="H1434" s="8" t="n"/>
       <c r="I1434" s="7" t="n">
-        <v>1100</v>
+        <v>94</v>
       </c>
       <c r="J1434" s="9" t="inlineStr">
         <is>
@@ -80033,12 +80018,12 @@
       </c>
       <c r="K1434" s="10" t="inlineStr">
         <is>
-          <t>genesis_tardia_2026-07_CONVENIO_H1_2</t>
+          <t>genesis_tardia_2026-07_CONVENIO_C_35</t>
         </is>
       </c>
       <c r="L1434" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:39</t>
+          <t>2026-07-30 11:47:42</t>
         </is>
       </c>
       <c r="M1434" s="9" t="inlineStr">
@@ -80050,12 +80035,12 @@
     <row r="1435">
       <c r="A1435" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B1435" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C1435" s="6" t="inlineStr">
@@ -80074,12 +80059,12 @@
         </is>
       </c>
       <c r="F1435" s="7" t="n">
-        <v>263</v>
+        <v>676</v>
       </c>
       <c r="G1435" s="8" t="n"/>
       <c r="H1435" s="8" t="n"/>
       <c r="I1435" s="7" t="n">
-        <v>263</v>
+        <v>676</v>
       </c>
       <c r="J1435" s="9" t="inlineStr">
         <is>
@@ -80088,12 +80073,12 @@
       </c>
       <c r="K1435" s="10" t="inlineStr">
         <is>
-          <t>genesis_tardia_2026-07_CONVENIO_B_20</t>
+          <t>genesis_tardia_2026-07_CONVENIO_F1_11</t>
         </is>
       </c>
       <c r="L1435" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:40</t>
+          <t>2026-07-30 11:47:43</t>
         </is>
       </c>
       <c r="M1435" s="9" t="inlineStr">
@@ -80105,12 +80090,12 @@
     <row r="1436">
       <c r="A1436" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B1436" s="5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C1436" s="6" t="inlineStr">
@@ -80129,12 +80114,12 @@
         </is>
       </c>
       <c r="F1436" s="7" t="n">
-        <v>334</v>
+        <v>50</v>
       </c>
       <c r="G1436" s="8" t="n"/>
       <c r="H1436" s="8" t="n"/>
       <c r="I1436" s="7" t="n">
-        <v>334</v>
+        <v>50</v>
       </c>
       <c r="J1436" s="9" t="inlineStr">
         <is>
@@ -80143,12 +80128,12 @@
       </c>
       <c r="K1436" s="10" t="inlineStr">
         <is>
-          <t>genesis_tardia_2026-07_CONVENIO_C_43</t>
+          <t>genesis_tardia_2026-07_CONVENIO_G_21</t>
         </is>
       </c>
       <c r="L1436" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:41</t>
+          <t>2026-07-30 11:47:44</t>
         </is>
       </c>
       <c r="M1436" s="9" t="inlineStr">
@@ -80160,12 +80145,12 @@
     <row r="1437">
       <c r="A1437" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B1437" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C1437" s="6" t="inlineStr">
@@ -80184,12 +80169,12 @@
         </is>
       </c>
       <c r="F1437" s="7" t="n">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="G1437" s="8" t="n"/>
       <c r="H1437" s="8" t="n"/>
       <c r="I1437" s="7" t="n">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="J1437" s="9" t="inlineStr">
         <is>
@@ -80198,12 +80183,12 @@
       </c>
       <c r="K1437" s="10" t="inlineStr">
         <is>
-          <t>genesis_tardia_2026-07_CONVENIO_C_35</t>
+          <t>genesis_tardia_2026-07_CONVENIO_W_2</t>
         </is>
       </c>
       <c r="L1437" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:42</t>
+          <t>2026-07-30 11:47:45</t>
         </is>
       </c>
       <c r="M1437" s="9" t="inlineStr">
@@ -80215,122 +80200,122 @@
     <row r="1438">
       <c r="A1438" s="5" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B1438" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C1438" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1438" s="6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E1438" s="6" t="inlineStr">
         <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="F1438" s="7" t="n">
-        <v>676</v>
-      </c>
-      <c r="G1438" s="8" t="n"/>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1438" s="8" t="n"/>
+      <c r="G1438" s="7" t="n">
+        <v>19</v>
+      </c>
       <c r="H1438" s="8" t="n"/>
       <c r="I1438" s="7" t="n">
-        <v>676</v>
+        <v>31</v>
       </c>
       <c r="J1438" s="9" t="inlineStr">
         <is>
-          <t>genesis_tardia</t>
+          <t>5_cobranza</t>
         </is>
       </c>
       <c r="K1438" s="10" t="inlineStr">
         <is>
-          <t>genesis_tardia_2026-07_CONVENIO_F1_11</t>
+          <t>recon_2026-07_ACUERDOS_H_21_1785430329.460551</t>
         </is>
       </c>
       <c r="L1438" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:43</t>
+          <t>2026-07-30 11:52:10</t>
         </is>
       </c>
       <c r="M1438" s="9" t="inlineStr">
         <is>
-          <t>GENESIS</t>
+          <t>COBRANZA</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B1439" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C1439" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1439" s="6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E1439" s="6" t="inlineStr">
         <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="F1439" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G1439" s="8" t="n"/>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1439" s="8" t="n"/>
+      <c r="G1439" s="7" t="n">
+        <v>29</v>
+      </c>
       <c r="H1439" s="8" t="n"/>
       <c r="I1439" s="7" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="J1439" s="9" t="inlineStr">
         <is>
-          <t>genesis_tardia</t>
+          <t>5_cobranza</t>
         </is>
       </c>
       <c r="K1439" s="10" t="inlineStr">
         <is>
-          <t>genesis_tardia_2026-07_CONVENIO_G_21</t>
+          <t>recon_2026-07_ACUERDOS_N_6_1785430470.140824</t>
         </is>
       </c>
       <c r="L1439" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:44</t>
+          <t>2026-07-30 11:54:30</t>
         </is>
       </c>
       <c r="M1439" s="9" t="inlineStr">
         <is>
-          <t>GENESIS</t>
+          <t>COBRANZA</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B1440" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C1440" s="6" t="inlineStr">
@@ -80340,52 +80325,52 @@
       </c>
       <c r="D1440" s="6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E1440" s="6" t="inlineStr">
         <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="F1440" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G1440" s="8" t="n"/>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1440" s="8" t="n"/>
+      <c r="G1440" s="7" t="n">
+        <v>58</v>
+      </c>
       <c r="H1440" s="8" t="n"/>
       <c r="I1440" s="7" t="n">
-        <v>50</v>
+        <v>-58</v>
       </c>
       <c r="J1440" s="9" t="inlineStr">
         <is>
-          <t>genesis_tardia</t>
+          <t>5_cobranza</t>
         </is>
       </c>
       <c r="K1440" s="10" t="inlineStr">
         <is>
-          <t>genesis_tardia_2026-07_CONVENIO_W_2</t>
+          <t>recon_2026-07_CONVENIO_P_6_1785430526.25186</t>
         </is>
       </c>
       <c r="L1440" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:45</t>
+          <t>2026-07-30 11:55:27</t>
         </is>
       </c>
       <c r="M1440" s="9" t="inlineStr">
         <is>
-          <t>GENESIS</t>
+          <t>COBRANZA</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B1441" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1441" s="6" t="inlineStr">
@@ -80418,12 +80403,12 @@
       </c>
       <c r="K1441" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_MULTA_C_21_1785430146.110605</t>
+          <t>recon_2026-07_MULTA_Q_4_1785431023.3108</t>
         </is>
       </c>
       <c r="L1441" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:49:06</t>
+          <t>2026-07-30 12:03:44</t>
         </is>
       </c>
       <c r="M1441" s="9" t="inlineStr">
@@ -80435,12 +80420,12 @@
     <row r="1442">
       <c r="A1442" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B1442" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1442" s="6" t="inlineStr">
@@ -80455,16 +80440,16 @@
       </c>
       <c r="E1442" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>AJUSTE</t>
         </is>
       </c>
       <c r="F1442" s="8" t="n"/>
-      <c r="G1442" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="H1442" s="8" t="n"/>
+      <c r="G1442" s="8" t="n"/>
+      <c r="H1442" s="7" t="n">
+        <v>-75</v>
+      </c>
       <c r="I1442" s="7" t="n">
-        <v>31</v>
+        <v>-75</v>
       </c>
       <c r="J1442" s="9" t="inlineStr">
         <is>
@@ -80473,34 +80458,34 @@
       </c>
       <c r="K1442" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_ACUERDOS_H_21_1785430329.460551</t>
+          <t>recon_2026-07_ACUERDOS_Q_4_1785431025.286066</t>
         </is>
       </c>
       <c r="L1442" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:10</t>
+          <t>2026-07-30 12:03:46</t>
         </is>
       </c>
       <c r="M1442" s="9" t="inlineStr">
         <is>
-          <t>COBRANZA</t>
+          <t>CORRECCION_SISTEMA</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B1443" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1443" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1443" s="6" t="inlineStr">
@@ -80510,52 +80495,52 @@
       </c>
       <c r="E1443" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>AJUSTE</t>
         </is>
       </c>
       <c r="F1443" s="8" t="n"/>
-      <c r="G1443" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="H1443" s="8" t="n"/>
+      <c r="G1443" s="8" t="n"/>
+      <c r="H1443" s="7" t="n">
+        <v>100</v>
+      </c>
       <c r="I1443" s="7" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J1443" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1443" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_ACUERDOS_N_6_1785430470.140824</t>
+          <t>notas_2026-07|Q-4-MULTA-revertir-condonacion-fallida</t>
         </is>
       </c>
       <c r="L1443" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:30</t>
+          <t>2026-07-30 13:21:58</t>
         </is>
       </c>
       <c r="M1443" s="9" t="inlineStr">
         <is>
-          <t>COBRANZA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" s="5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B1444" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1444" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1444" s="6" t="inlineStr">
@@ -80565,42 +80550,42 @@
       </c>
       <c r="E1444" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>AJUSTE</t>
         </is>
       </c>
       <c r="F1444" s="8" t="n"/>
-      <c r="G1444" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="H1444" s="8" t="n"/>
+      <c r="G1444" s="8" t="n"/>
+      <c r="H1444" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="I1444" s="7" t="n">
-        <v>-58</v>
+        <v>75</v>
       </c>
       <c r="J1444" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1444" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_CONVENIO_P_6_1785430526.25186</t>
+          <t>notas_2026-07|Q-4-ACUERDOS-revertir-condonacion-fallida</t>
         </is>
       </c>
       <c r="L1444" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 11:55:27</t>
+          <t>2026-07-30 13:21:59</t>
         </is>
       </c>
       <c r="M1444" s="9" t="inlineStr">
         <is>
-          <t>COBRANZA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" s="5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B1445" s="5" t="inlineStr">
@@ -80610,7 +80595,7 @@
       </c>
       <c r="C1445" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1445" s="6" t="inlineStr">
@@ -80626,46 +80611,46 @@
       <c r="F1445" s="8" t="n"/>
       <c r="G1445" s="8" t="n"/>
       <c r="H1445" s="7" t="n">
-        <v>-50</v>
+        <v>58</v>
       </c>
       <c r="I1445" s="7" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="J1445" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1445" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_MULTA_J_6_1785430997.967522</t>
+          <t>notas_2026-07|P-6-CONVENIO-pago-real-estable-30072026</t>
         </is>
       </c>
       <c r="L1445" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 12:03:18</t>
+          <t>2026-07-30 14:04:20</t>
         </is>
       </c>
       <c r="M1445" s="9" t="inlineStr">
         <is>
-          <t>CORRECCION_SISTEMA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" s="5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B1446" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C1446" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1446" s="6" t="inlineStr">
@@ -80681,29 +80666,29 @@
       <c r="F1446" s="8" t="n"/>
       <c r="G1446" s="8" t="n"/>
       <c r="H1446" s="7" t="n">
-        <v>-75</v>
+        <v>25</v>
       </c>
       <c r="I1446" s="7" t="n">
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="J1446" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1446" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_ACUERDOS_J_6_1785430999.73768</t>
+          <t>notas_2026-07|Q-5-CONVENIO-condonacion-estable-30072026</t>
         </is>
       </c>
       <c r="L1446" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 12:03:20</t>
+          <t>2026-07-30 14:26:23</t>
         </is>
       </c>
       <c r="M1446" s="9" t="inlineStr">
         <is>
-          <t>CORRECCION_SISTEMA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
@@ -80715,12 +80700,12 @@
       </c>
       <c r="B1447" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C1447" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1447" s="6" t="inlineStr">
@@ -80739,26 +80724,26 @@
         <v>-50</v>
       </c>
       <c r="I1447" s="7" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="J1447" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1447" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_MULTA_Q_4_1785431023.3108</t>
+          <t>notas_2026-07|Q-5-CONVENIO-correccion-de-signo-30072026</t>
         </is>
       </c>
       <c r="L1447" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 12:03:44</t>
+          <t>2026-07-30 14:26:36</t>
         </is>
       </c>
       <c r="M1447" s="9" t="inlineStr">
         <is>
-          <t>CORRECCION_SISTEMA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
@@ -80775,7 +80760,7 @@
       </c>
       <c r="C1448" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1448" s="6" t="inlineStr">
@@ -80791,46 +80776,46 @@
       <c r="F1448" s="8" t="n"/>
       <c r="G1448" s="8" t="n"/>
       <c r="H1448" s="7" t="n">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I1448" s="7" t="n">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="J1448" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1448" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_ACUERDOS_Q_4_1785431025.286066</t>
+          <t>notas_2026-07|Q-4-MULTA-recondonacion-definitiva-30072026</t>
         </is>
       </c>
       <c r="L1448" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 12:03:46</t>
+          <t>2026-07-30 20:31:38</t>
         </is>
       </c>
       <c r="M1448" s="9" t="inlineStr">
         <is>
-          <t>CORRECCION_SISTEMA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B1449" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1449" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1449" s="6" t="inlineStr">
@@ -80846,10 +80831,10 @@
       <c r="F1449" s="8" t="n"/>
       <c r="G1449" s="8" t="n"/>
       <c r="H1449" s="7" t="n">
-        <v>100</v>
+        <v>-75</v>
       </c>
       <c r="I1449" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J1449" s="9" t="inlineStr">
         <is>
@@ -80858,12 +80843,12 @@
       </c>
       <c r="K1449" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|C-21-MULTA-revertir-condonacion-fallida</t>
+          <t>notas_2026-07|Q-4-ACUERDOS-recondonacion-definitiva-30072026</t>
         </is>
       </c>
       <c r="L1449" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21:56</t>
+          <t>2026-07-30 20:31:39</t>
         </is>
       </c>
       <c r="M1449" s="9" t="inlineStr">
@@ -80875,17 +80860,17 @@
     <row r="1450">
       <c r="A1450" s="5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B1450" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C1450" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1450" s="6" t="inlineStr">
@@ -80895,16 +80880,16 @@
       </c>
       <c r="E1450" s="6" t="inlineStr">
         <is>
-          <t>AJUSTE</t>
+          <t>PAGO</t>
         </is>
       </c>
       <c r="F1450" s="8" t="n"/>
-      <c r="G1450" s="8" t="n"/>
-      <c r="H1450" s="7" t="n">
-        <v>100</v>
-      </c>
+      <c r="G1450" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1450" s="8" t="n"/>
       <c r="I1450" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J1450" s="9" t="inlineStr">
         <is>
@@ -80913,29 +80898,34 @@
       </c>
       <c r="K1450" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|J-6-MULTA-revertir-condonacion-fallida</t>
+          <t>notas_2026-07|T-7-CONVENIO</t>
         </is>
       </c>
       <c r="L1450" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21:57</t>
+          <t>2026-07-31 15:51:27</t>
         </is>
       </c>
       <c r="M1450" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>DECLARACION_SECRETARIA</t>
+        </is>
+      </c>
+      <c r="N1450" t="inlineStr">
+        <is>
+          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" s="5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B1451" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C1451" s="6" t="inlineStr">
@@ -80950,16 +80940,16 @@
       </c>
       <c r="E1451" s="6" t="inlineStr">
         <is>
-          <t>AJUSTE</t>
+          <t>PAGO</t>
         </is>
       </c>
       <c r="F1451" s="8" t="n"/>
-      <c r="G1451" s="8" t="n"/>
-      <c r="H1451" s="7" t="n">
-        <v>150</v>
-      </c>
+      <c r="G1451" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H1451" s="8" t="n"/>
       <c r="I1451" s="7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J1451" s="9" t="inlineStr">
         <is>
@@ -80968,29 +80958,34 @@
       </c>
       <c r="K1451" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|J-6-ACUERDOS-revertir-condonacion-fallida</t>
+          <t>notas_2026-07|T-7-ACUERDOS</t>
         </is>
       </c>
       <c r="L1451" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21:57</t>
+          <t>2026-07-31 15:51:28</t>
         </is>
       </c>
       <c r="M1451" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>DECLARACION_SECRETARIA</t>
+        </is>
+      </c>
+      <c r="N1451" t="inlineStr">
+        <is>
+          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" s="5" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B1452" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C1452" s="6" t="inlineStr">
@@ -81011,10 +81006,10 @@
       <c r="F1452" s="8" t="n"/>
       <c r="G1452" s="8" t="n"/>
       <c r="H1452" s="7" t="n">
-        <v>100</v>
+        <v>-30</v>
       </c>
       <c r="I1452" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J1452" s="9" t="inlineStr">
         <is>
@@ -81023,12 +81018,12 @@
       </c>
       <c r="K1452" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|Q-4-MULTA-revertir-condonacion-fallida</t>
+          <t>notas_2026-07|F1-10-MULTA</t>
         </is>
       </c>
       <c r="L1452" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21:58</t>
+          <t>2026-07-31 16:22:28</t>
         </is>
       </c>
       <c r="M1452" s="9" t="inlineStr">
@@ -81040,17 +81035,17 @@
     <row r="1453">
       <c r="A1453" s="5" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B1453" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C1453" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1453" s="6" t="inlineStr">
@@ -81066,10 +81061,10 @@
       <c r="F1453" s="8" t="n"/>
       <c r="G1453" s="8" t="n"/>
       <c r="H1453" s="7" t="n">
-        <v>150</v>
+        <v>-50</v>
       </c>
       <c r="I1453" s="7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J1453" s="9" t="inlineStr">
         <is>
@@ -81078,12 +81073,12 @@
       </c>
       <c r="K1453" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|Q-4-ACUERDOS-revertir-condonacion-fallida</t>
+          <t>notas_2026-07|C-19-MULTA</t>
         </is>
       </c>
       <c r="L1453" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21:59</t>
+          <t>2026-07-31 16:22:29</t>
         </is>
       </c>
       <c r="M1453" s="9" t="inlineStr">
@@ -81095,17 +81090,17 @@
     <row r="1454">
       <c r="A1454" s="5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B1454" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C1454" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1454" s="6" t="inlineStr">
@@ -81121,7 +81116,7 @@
       <c r="F1454" s="8" t="n"/>
       <c r="G1454" s="8" t="n"/>
       <c r="H1454" s="7" t="n">
-        <v>58</v>
+        <v>-12</v>
       </c>
       <c r="I1454" s="7" t="n">
         <v>0</v>
@@ -81133,12 +81128,12 @@
       </c>
       <c r="K1454" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|P-6-CONVENIO-pago-real-estable-30072026</t>
+          <t>notas_2026-07|R-5-MULTA</t>
         </is>
       </c>
       <c r="L1454" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 14:04:20</t>
+          <t>2026-07-31 16:22:30</t>
         </is>
       </c>
       <c r="M1454" s="9" t="inlineStr">
@@ -81150,7 +81145,7 @@
     <row r="1455">
       <c r="A1455" s="5" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B1455" s="5" t="inlineStr">
@@ -81160,7 +81155,7 @@
       </c>
       <c r="C1455" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1455" s="6" t="inlineStr">
@@ -81170,16 +81165,16 @@
       </c>
       <c r="E1455" s="6" t="inlineStr">
         <is>
-          <t>AJUSTE</t>
+          <t>PAGO</t>
         </is>
       </c>
       <c r="F1455" s="8" t="n"/>
-      <c r="G1455" s="8" t="n"/>
-      <c r="H1455" s="7" t="n">
-        <v>25</v>
-      </c>
+      <c r="G1455" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1455" s="8" t="n"/>
       <c r="I1455" s="7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1455" s="9" t="inlineStr">
         <is>
@@ -81188,29 +81183,34 @@
       </c>
       <c r="K1455" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|Q-5-CONVENIO-condonacion-estable-30072026</t>
+          <t>notas_2026-07|S-5-ACUERDOS</t>
         </is>
       </c>
       <c r="L1455" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 14:26:23</t>
+          <t>2026-07-31 16:22:32</t>
         </is>
       </c>
       <c r="M1455" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>DECLARACION_SECRETARIA</t>
+        </is>
+      </c>
+      <c r="N1455" t="inlineStr">
+        <is>
+          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" s="5" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B1456" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C1456" s="6" t="inlineStr">
@@ -81225,14 +81225,14 @@
       </c>
       <c r="E1456" s="6" t="inlineStr">
         <is>
-          <t>AJUSTE</t>
+          <t>PAGO</t>
         </is>
       </c>
       <c r="F1456" s="8" t="n"/>
-      <c r="G1456" s="8" t="n"/>
-      <c r="H1456" s="7" t="n">
-        <v>-50</v>
-      </c>
+      <c r="G1456" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1456" s="8" t="n"/>
       <c r="I1456" s="7" t="n">
         <v>0</v>
       </c>
@@ -81243,34 +81243,39 @@
       </c>
       <c r="K1456" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|Q-5-CONVENIO-correccion-de-signo-30072026</t>
+          <t>notas_2026-07|G-18-CONVENIO</t>
         </is>
       </c>
       <c r="L1456" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 14:26:36</t>
+          <t>2026-07-31 16:47:19</t>
         </is>
       </c>
       <c r="M1456" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>DECLARACION_SECRETARIA</t>
+        </is>
+      </c>
+      <c r="N1456" t="inlineStr">
+        <is>
+          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" s="5" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B1457" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C1457" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1457" s="6" t="inlineStr">
@@ -81280,52 +81285,52 @@
       </c>
       <c r="E1457" s="6" t="inlineStr">
         <is>
-          <t>AJUSTE</t>
+          <t>PAGO</t>
         </is>
       </c>
       <c r="F1457" s="8" t="n"/>
-      <c r="G1457" s="8" t="n"/>
-      <c r="H1457" s="7" t="n">
-        <v>-50</v>
-      </c>
+      <c r="G1457" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1457" s="8" t="n"/>
       <c r="I1457" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1457" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>5_cobranza</t>
         </is>
       </c>
       <c r="K1457" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|Q-4-MULTA-recondonacion-definitiva-30072026</t>
+          <t>recon_2026-07_CONVENIO_A_6_1785539301.825676</t>
         </is>
       </c>
       <c r="L1457" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 20:31:38</t>
+          <t>2026-07-31 18:08:23</t>
         </is>
       </c>
       <c r="M1457" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>COBRANZA</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" s="5" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B1458" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C1458" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1458" s="6" t="inlineStr">
@@ -81335,52 +81340,52 @@
       </c>
       <c r="E1458" s="6" t="inlineStr">
         <is>
-          <t>AJUSTE</t>
+          <t>PAGO</t>
         </is>
       </c>
       <c r="F1458" s="8" t="n"/>
-      <c r="G1458" s="8" t="n"/>
-      <c r="H1458" s="7" t="n">
-        <v>-75</v>
-      </c>
+      <c r="G1458" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1458" s="8" t="n"/>
       <c r="I1458" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J1458" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>5_cobranza</t>
         </is>
       </c>
       <c r="K1458" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|Q-4-ACUERDOS-recondonacion-definitiva-30072026</t>
+          <t>recon_2026-07_CONVENIO_D_1_1785539498.920724</t>
         </is>
       </c>
       <c r="L1458" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30 20:31:39</t>
+          <t>2026-07-31 18:11:40</t>
         </is>
       </c>
       <c r="M1458" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>COBRANZA</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" s="5" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B1459" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C1459" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1459" s="6" t="inlineStr">
@@ -81390,57 +81395,52 @@
       </c>
       <c r="E1459" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>AJUSTE</t>
         </is>
       </c>
       <c r="F1459" s="8" t="n"/>
-      <c r="G1459" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H1459" s="8" t="n"/>
+      <c r="G1459" s="8" t="n"/>
+      <c r="H1459" s="7" t="n">
+        <v>-25</v>
+      </c>
       <c r="I1459" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J1459" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>5_cobranza</t>
         </is>
       </c>
       <c r="K1459" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|T-7-CONVENIO</t>
+          <t>recon_2026-07_ACUERDOS_D_16_1785539537.682805</t>
         </is>
       </c>
       <c r="L1459" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 15:51:27</t>
+          <t>2026-07-31 18:12:19</t>
         </is>
       </c>
       <c r="M1459" s="9" t="inlineStr">
         <is>
-          <t>DECLARACION_SECRETARIA</t>
-        </is>
-      </c>
-      <c r="N1459" t="inlineStr">
-        <is>
-          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
+          <t>CORRECCION_SISTEMA</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" s="5" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B1460" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C1460" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1460" s="6" t="inlineStr">
@@ -81455,47 +81455,42 @@
       </c>
       <c r="F1460" s="8" t="n"/>
       <c r="G1460" s="7" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H1460" s="8" t="n"/>
       <c r="I1460" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J1460" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>5_cobranza</t>
         </is>
       </c>
       <c r="K1460" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|T-7-ACUERDOS</t>
+          <t>recon_2026-07_CONVENIO_D_16_1785539540.284214</t>
         </is>
       </c>
       <c r="L1460" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 15:51:28</t>
+          <t>2026-07-31 18:12:21</t>
         </is>
       </c>
       <c r="M1460" s="9" t="inlineStr">
         <is>
-          <t>DECLARACION_SECRETARIA</t>
-        </is>
-      </c>
-      <c r="N1460" t="inlineStr">
-        <is>
-          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
+          <t>COBRANZA</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" s="5" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B1461" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C1461" s="6" t="inlineStr">
@@ -81505,7 +81500,7 @@
       </c>
       <c r="D1461" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E1461" s="6" t="inlineStr">
@@ -81516,10 +81511,10 @@
       <c r="F1461" s="8" t="n"/>
       <c r="G1461" s="8" t="n"/>
       <c r="H1461" s="7" t="n">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="I1461" s="7" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="J1461" s="9" t="inlineStr">
         <is>
@@ -81528,12 +81523,12 @@
       </c>
       <c r="K1461" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|F1-10-MULTA</t>
+          <t>notas_2026-07|F-12-MULTA-redirigido-31072026</t>
         </is>
       </c>
       <c r="L1461" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 16:22:28</t>
+          <t>2026-07-31 18:29:26</t>
         </is>
       </c>
       <c r="M1461" s="9" t="inlineStr">
@@ -81545,12 +81540,12 @@
     <row r="1462">
       <c r="A1462" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B1462" s="5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C1462" s="6" t="inlineStr">
@@ -81560,7 +81555,7 @@
       </c>
       <c r="D1462" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E1462" s="6" t="inlineStr">
@@ -81571,7 +81566,7 @@
       <c r="F1462" s="8" t="n"/>
       <c r="G1462" s="8" t="n"/>
       <c r="H1462" s="7" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I1462" s="7" t="n">
         <v>0</v>
@@ -81583,12 +81578,12 @@
       </c>
       <c r="K1462" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|C-19-MULTA</t>
+          <t>notas_2026-07|F-12-MULTA-estabilizador-31072026</t>
         </is>
       </c>
       <c r="L1462" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 16:22:29</t>
+          <t>2026-07-31 18:29:27</t>
         </is>
       </c>
       <c r="M1462" s="9" t="inlineStr">
@@ -81600,34 +81595,34 @@
     <row r="1463">
       <c r="A1463" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B1463" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C1463" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1463" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E1463" s="6" t="inlineStr">
         <is>
-          <t>AJUSTE</t>
+          <t>PAGO</t>
         </is>
       </c>
       <c r="F1463" s="8" t="n"/>
-      <c r="G1463" s="8" t="n"/>
-      <c r="H1463" s="7" t="n">
-        <v>-12</v>
-      </c>
+      <c r="G1463" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1463" s="8" t="n"/>
       <c r="I1463" s="7" t="n">
         <v>0</v>
       </c>
@@ -81638,53 +81633,58 @@
       </c>
       <c r="K1463" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|R-5-MULTA</t>
+          <t>notas_2026-07|F-12-CONVENIO-redirigido-31072026</t>
         </is>
       </c>
       <c r="L1463" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 16:22:30</t>
+          <t>2026-07-31 18:29:28</t>
         </is>
       </c>
       <c r="M1463" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>DECLARACION_SECRETARIA</t>
+        </is>
+      </c>
+      <c r="N1463" t="inlineStr">
+        <is>
+          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B1464" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C1464" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1464" s="6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E1464" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>AJUSTE</t>
         </is>
       </c>
       <c r="F1464" s="8" t="n"/>
-      <c r="G1464" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H1464" s="8" t="n"/>
+      <c r="G1464" s="8" t="n"/>
+      <c r="H1464" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="I1464" s="7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1464" s="9" t="inlineStr">
         <is>
@@ -81693,34 +81693,29 @@
       </c>
       <c r="K1464" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|S-5-ACUERDOS</t>
+          <t>notas_2026-07|F-12-CONVENIO-correccion-etiqueta-31072026</t>
         </is>
       </c>
       <c r="L1464" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 16:22:32</t>
+          <t>2026-07-31 18:31:15</t>
         </is>
       </c>
       <c r="M1464" s="9" t="inlineStr">
         <is>
-          <t>DECLARACION_SECRETARIA</t>
-        </is>
-      </c>
-      <c r="N1464" t="inlineStr">
-        <is>
-          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B1465" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C1465" s="6" t="inlineStr">
@@ -81740,7 +81735,7 @@
       </c>
       <c r="F1465" s="8" t="n"/>
       <c r="G1465" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H1465" s="8" t="n"/>
       <c r="I1465" s="7" t="n">
@@ -81753,12 +81748,12 @@
       </c>
       <c r="K1465" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|G-18-CONVENIO</t>
+          <t>notas_2026-07|F-12-CONVENIO-redirigido-31072026-v2</t>
         </is>
       </c>
       <c r="L1465" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 16:47:19</t>
+          <t>2026-07-31 18:31:16</t>
         </is>
       </c>
       <c r="M1465" s="9" t="inlineStr">
@@ -81775,17 +81770,17 @@
     <row r="1466">
       <c r="A1466" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B1466" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C1466" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1466" s="6" t="inlineStr">
@@ -81795,52 +81790,52 @@
       </c>
       <c r="E1466" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>AJUSTE</t>
         </is>
       </c>
       <c r="F1466" s="8" t="n"/>
-      <c r="G1466" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="H1466" s="8" t="n"/>
+      <c r="G1466" s="8" t="n"/>
+      <c r="H1466" s="7" t="n">
+        <v>-30</v>
+      </c>
       <c r="I1466" s="7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J1466" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1466" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_CONVENIO_A_6_1785539301.825676</t>
+          <t>notas_2026-07|C1-17-MULTA-duplicado-31072026</t>
         </is>
       </c>
       <c r="L1466" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:08:23</t>
+          <t>2026-07-31 19:58:08</t>
         </is>
       </c>
       <c r="M1466" s="9" t="inlineStr">
         <is>
-          <t>COBRANZA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B1467" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29A</t>
         </is>
       </c>
       <c r="C1467" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1467" s="6" t="inlineStr">
@@ -81850,42 +81845,42 @@
       </c>
       <c r="E1467" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>AJUSTE</t>
         </is>
       </c>
       <c r="F1467" s="8" t="n"/>
-      <c r="G1467" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H1467" s="8" t="n"/>
+      <c r="G1467" s="8" t="n"/>
+      <c r="H1467" s="7" t="n">
+        <v>-20</v>
+      </c>
       <c r="I1467" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J1467" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1467" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_CONVENIO_D_1_1785539498.920724</t>
+          <t>notas_2026-07|C-29A-MULTA-duplicado-31072026</t>
         </is>
       </c>
       <c r="L1467" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:11:40</t>
+          <t>2026-07-31 19:58:08</t>
         </is>
       </c>
       <c r="M1467" s="9" t="inlineStr">
         <is>
-          <t>COBRANZA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B1468" s="5" t="inlineStr">
@@ -81911,46 +81906,46 @@
       <c r="F1468" s="8" t="n"/>
       <c r="G1468" s="8" t="n"/>
       <c r="H1468" s="7" t="n">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="I1468" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J1468" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1468" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_ACUERDOS_D_16_1785539537.682805</t>
+          <t>notas_2026-07|Q-16-ACUERDOS-duplicado-31072026</t>
         </is>
       </c>
       <c r="L1468" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:12:19</t>
+          <t>2026-07-31 19:58:09</t>
         </is>
       </c>
       <c r="M1468" s="9" t="inlineStr">
         <is>
-          <t>CORRECCION_SISTEMA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B1469" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C1469" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1469" s="6" t="inlineStr">
@@ -81960,57 +81955,57 @@
       </c>
       <c r="E1469" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>AJUSTE</t>
         </is>
       </c>
       <c r="F1469" s="8" t="n"/>
-      <c r="G1469" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="H1469" s="8" t="n"/>
+      <c r="G1469" s="8" t="n"/>
+      <c r="H1469" s="7" t="n">
+        <v>-50</v>
+      </c>
       <c r="I1469" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J1469" s="9" t="inlineStr">
         <is>
-          <t>5_cobranza</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1469" s="10" t="inlineStr">
         <is>
-          <t>recon_2026-07_CONVENIO_D_16_1785539540.284214</t>
+          <t>notas_2026-07|S-14-MULTA-duplicado-31072026</t>
         </is>
       </c>
       <c r="L1469" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:12:21</t>
+          <t>2026-07-31 19:58:10</t>
         </is>
       </c>
       <c r="M1469" s="9" t="inlineStr">
         <is>
-          <t>COBRANZA</t>
+          <t>SIN_CLASIFICAR</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B1470" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C1470" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1470" s="6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E1470" s="6" t="inlineStr">
@@ -82021,10 +82016,10 @@
       <c r="F1470" s="8" t="n"/>
       <c r="G1470" s="8" t="n"/>
       <c r="H1470" s="7" t="n">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I1470" s="7" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="J1470" s="9" t="inlineStr">
         <is>
@@ -82033,12 +82028,12 @@
       </c>
       <c r="K1470" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|F-12-MULTA-redirigido-31072026</t>
+          <t>notas_2026-07|S-14-ACUERDOS-duplicado-31072026</t>
         </is>
       </c>
       <c r="L1470" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:29:26</t>
+          <t>2026-07-31 19:58:11</t>
         </is>
       </c>
       <c r="M1470" s="9" t="inlineStr">
@@ -82050,12 +82045,12 @@
     <row r="1471">
       <c r="A1471" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B1471" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C1471" s="6" t="inlineStr">
@@ -82065,7 +82060,7 @@
       </c>
       <c r="D1471" s="6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E1471" s="6" t="inlineStr">
@@ -82076,7 +82071,7 @@
       <c r="F1471" s="8" t="n"/>
       <c r="G1471" s="8" t="n"/>
       <c r="H1471" s="7" t="n">
-        <v>50</v>
+        <v>-20</v>
       </c>
       <c r="I1471" s="7" t="n">
         <v>0</v>
@@ -82088,51 +82083,56 @@
       </c>
       <c r="K1471" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|F-12-MULTA-estabilizador-31072026</t>
+          <t>reclamos_2026-08-01|J-1-MULTA</t>
         </is>
       </c>
       <c r="L1471" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:29:27</t>
+          <t>2026-08-03 12:05:47</t>
         </is>
       </c>
       <c r="M1471" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+      <c r="N1471" s="10" t="inlineStr">
+        <is>
+          <t>exonerado por la directiva 01/08/2026 — multa faena y reunion (Comedor Popular Club de Madres)</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B1472" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C1472" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1472" s="6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E1472" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>AJUSTE</t>
         </is>
       </c>
       <c r="F1472" s="8" t="n"/>
-      <c r="G1472" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H1472" s="8" t="n"/>
+      <c r="G1472" s="8" t="n"/>
+      <c r="H1472" s="7" t="n">
+        <v>-75</v>
+      </c>
       <c r="I1472" s="7" t="n">
         <v>0</v>
       </c>
@@ -82143,44 +82143,44 @@
       </c>
       <c r="K1472" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|F-12-CONVENIO-redirigido-31072026</t>
+          <t>reclamos_2026-08-01|J-1-ACUERDOS</t>
         </is>
       </c>
       <c r="L1472" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:29:28</t>
+          <t>2026-08-03 12:05:49</t>
         </is>
       </c>
       <c r="M1472" s="9" t="inlineStr">
         <is>
-          <t>DECLARACION_SECRETARIA</t>
-        </is>
-      </c>
-      <c r="N1472" t="inlineStr">
-        <is>
-          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+      <c r="N1472" s="10" t="inlineStr">
+        <is>
+          <t>exonerado por la directiva 01/08/2026 — techado y campo (Comedor Popular Club de Madres)</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B1473" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C1473" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1473" s="6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E1473" s="6" t="inlineStr">
@@ -82191,10 +82191,10 @@
       <c r="F1473" s="8" t="n"/>
       <c r="G1473" s="8" t="n"/>
       <c r="H1473" s="7" t="n">
-        <v>50</v>
+        <v>-30</v>
       </c>
       <c r="I1473" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J1473" s="9" t="inlineStr">
         <is>
@@ -82203,24 +82203,29 @@
       </c>
       <c r="K1473" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|F-12-CONVENIO-correccion-etiqueta-31072026</t>
+          <t>reclamos_2026-08-01|O-2-MULTA</t>
         </is>
       </c>
       <c r="L1473" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:31:15</t>
+          <t>2026-08-03 12:05:52</t>
         </is>
       </c>
       <c r="M1473" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+      <c r="N1473" s="10" t="inlineStr">
+        <is>
+          <t>exonerado por la directiva 01/08/2026 — se exonera la multa (Carmen Ingaruca Julca)</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B1474" s="5" t="inlineStr">
@@ -82240,57 +82245,57 @@
       </c>
       <c r="E1474" s="6" t="inlineStr">
         <is>
-          <t>PAGO</t>
-        </is>
-      </c>
-      <c r="F1474" s="8" t="n"/>
-      <c r="G1474" s="7" t="n">
-        <v>50</v>
-      </c>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="F1474" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G1474" s="8" t="n"/>
       <c r="H1474" s="8" t="n"/>
       <c r="I1474" s="7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J1474" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>genesis_tardia</t>
         </is>
       </c>
       <c r="K1474" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|F-12-CONVENIO-redirigido-31072026-v2</t>
+          <t>reclamos_2026-08-01|M-12-CONVENIO</t>
         </is>
       </c>
       <c r="L1474" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:31:16</t>
+          <t>2026-08-03 13:51:06</t>
         </is>
       </c>
       <c r="M1474" s="9" t="inlineStr">
         <is>
-          <t>DECLARACION_SECRETARIA</t>
-        </is>
-      </c>
-      <c r="N1474" t="inlineStr">
-        <is>
-          <t>Pago DECLARADO por la secretaria (notas_2026-07): dijo que el vecino ya pago. Se escribio como registrar_pago directo en el ledger porque los precursores (abonos_rezagados/ajustes_cargo) no llegan al ledger de MULTA/ACUERDOS cuando no hay plata real del ciclo — ver docs/RETOMAR_notas_secretaria_julio_grupo2_2026-07-29.md seccion 3.1. PENDIENTE: investigar si esa plata es un EXCESO que ya estaba en caja (entonces la clase final es DECLARACION y no suma a caja) o un pago nuevo que hay que sembrar en abonos_rezagados.xlsx (entonces es ABONO_REZAGADO y si suma). Mientras tanto NO suma a caja.</t>
+          <t>GENESIS</t>
+        </is>
+      </c>
+      <c r="N1474" s="10" t="inlineStr">
+        <is>
+          <t>Cargo nuevo de convenio S/80 confirmado por la directiva el 01/08/2026 (corrige el campo: se habia sembrado en MANTENIMIENTO el 28/07). SOLO REGISTRO: el efecto lo hace el CARGO del ledger — esta fila es para el backfill del libro_mayor.</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" s="5" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B1475" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14A</t>
         </is>
       </c>
       <c r="C1475" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1475" s="6" t="inlineStr">
@@ -82306,46 +82311,51 @@
       <c r="F1475" s="8" t="n"/>
       <c r="G1475" s="8" t="n"/>
       <c r="H1475" s="7" t="n">
-        <v>-30</v>
+        <v>-75</v>
       </c>
       <c r="I1475" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J1475" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>reidentificacion_cargo</t>
         </is>
       </c>
       <c r="K1475" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|C1-17-MULTA-duplicado-31072026</t>
+          <t>reidentificacion_cargo|E-14A-a-E-14B|ACUERDOS|origen</t>
         </is>
       </c>
       <c r="L1475" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 19:58:08</t>
+          <t>2026-08-03 16:13:52</t>
         </is>
       </c>
       <c r="M1475" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>REASIGNACION</t>
+        </is>
+      </c>
+      <c r="N1475" s="10" t="inlineStr">
+        <is>
+          <t>Cargo movido a E-14B. El cargo de techado y campo (75) de JUAN SAAVEDRA SAAVEDRA se sembro el 2026-07 sobre E-14A, lote que NO existe en padron_reconciliado. La fuente (DEUDORES Y PAGOS DEL TECHADO Y CAMPO, hoja Corregido) lo lista como E-14A; el padron lo tiene como E-14B. Consecuencia: E-14A imprimio boleta sin nombre (recibo 18083) y E-14B quedo sin cargo, lo que llevo a la directiva a pedir un cargo nuevo el 01/08 (habria duplicado los 75). Se mueve al lote real.</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B1476" s="5" t="inlineStr">
         <is>
-          <t>29A</t>
+          <t>14B</t>
         </is>
       </c>
       <c r="C1476" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1476" s="6" t="inlineStr">
@@ -82355,52 +82365,57 @@
       </c>
       <c r="E1476" s="6" t="inlineStr">
         <is>
-          <t>AJUSTE</t>
-        </is>
-      </c>
-      <c r="F1476" s="8" t="n"/>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="F1476" s="7" t="n">
+        <v>75</v>
+      </c>
       <c r="G1476" s="8" t="n"/>
-      <c r="H1476" s="7" t="n">
-        <v>-20</v>
-      </c>
+      <c r="H1476" s="8" t="n"/>
       <c r="I1476" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J1476" s="9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>reidentificacion_cargo</t>
         </is>
       </c>
       <c r="K1476" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|C-29A-MULTA-duplicado-31072026</t>
+          <t>reidentificacion_cargo|E-14A-a-E-14B|ACUERDOS|destino</t>
         </is>
       </c>
       <c r="L1476" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 19:58:08</t>
+          <t>2026-08-03 16:13:54</t>
         </is>
       </c>
       <c r="M1476" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>REASIGNACION</t>
+        </is>
+      </c>
+      <c r="N1476" s="10" t="inlineStr">
+        <is>
+          <t>Cargo recibido desde E-14A. El cargo de techado y campo (75) de JUAN SAAVEDRA SAAVEDRA se sembro el 2026-07 sobre E-14A, lote que NO existe en padron_reconciliado. La fuente (DEUDORES Y PAGOS DEL TECHADO Y CAMPO, hoja Corregido) lo lista como E-14A; el padron lo tiene como E-14B. Consecuencia: E-14A imprimio boleta sin nombre (recibo 18083) y E-14B quedo sin cargo, lo que llevo a la directiva a pedir un cargo nuevo el 01/08 (habria duplicado los 75). Se mueve al lote real.</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" s="5" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B1477" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1477" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1477" s="6" t="inlineStr">
@@ -82416,10 +82431,10 @@
       <c r="F1477" s="8" t="n"/>
       <c r="G1477" s="8" t="n"/>
       <c r="H1477" s="7" t="n">
-        <v>-75</v>
+        <v>25</v>
       </c>
       <c r="I1477" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J1477" s="9" t="inlineStr">
         <is>
@@ -82428,34 +82443,39 @@
       </c>
       <c r="K1477" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|Q-16-ACUERDOS-duplicado-31072026</t>
+          <t>reclamos_2026-08-01|G-4-MULTA-reasig</t>
         </is>
       </c>
       <c r="L1477" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 19:58:09</t>
+          <t>2026-08-03 17:30:25</t>
         </is>
       </c>
       <c r="M1477" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>REASIGNACION</t>
+        </is>
+      </c>
+      <c r="N1477" s="10" t="inlineStr">
+        <is>
+          <t>La secretaria confirma (01/08/2026) que su pago de MULTA de S/25 debe contarse contra CONVENIO. Se devuelve la deuda a MULTA y se acredita a CONVENIO. No hay plata nueva: es el mismo pago cambiando de concepto.</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B1478" s="5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1478" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1478" s="6" t="inlineStr">
@@ -82471,10 +82491,10 @@
       <c r="F1478" s="8" t="n"/>
       <c r="G1478" s="8" t="n"/>
       <c r="H1478" s="7" t="n">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="I1478" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J1478" s="9" t="inlineStr">
         <is>
@@ -82483,34 +82503,39 @@
       </c>
       <c r="K1478" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|S-14-MULTA-duplicado-31072026</t>
+          <t>reclamos_2026-08-01|G-4-CONVENIO-reasig</t>
         </is>
       </c>
       <c r="L1478" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 19:58:10</t>
+          <t>2026-08-03 17:30:27</t>
         </is>
       </c>
       <c r="M1478" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>REASIGNACION</t>
+        </is>
+      </c>
+      <c r="N1478" s="10" t="inlineStr">
+        <is>
+          <t>La secretaria confirma (01/08/2026) que su pago de MULTA de S/25 debe contarse contra CONVENIO. Se devuelve la deuda a MULTA y se acredita a CONVENIO. No hay plata nueva: es el mismo pago cambiando de concepto.</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B1479" s="5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C1479" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1479" s="6" t="inlineStr">
@@ -82526,7 +82551,7 @@
       <c r="F1479" s="8" t="n"/>
       <c r="G1479" s="8" t="n"/>
       <c r="H1479" s="7" t="n">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I1479" s="7" t="n">
         <v>0</v>
@@ -82538,29 +82563,34 @@
       </c>
       <c r="K1479" s="10" t="inlineStr">
         <is>
-          <t>notas_2026-07|S-14-ACUERDOS-duplicado-31072026</t>
+          <t>reclamos_2026-08-01|G-4-CONVENIO-abono</t>
         </is>
       </c>
       <c r="L1479" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31 19:58:11</t>
+          <t>2026-08-03 17:30:29</t>
         </is>
       </c>
       <c r="M1479" s="9" t="inlineStr">
         <is>
-          <t>SIN_CLASIFICAR</t>
+          <t>ABONO_REZAGADO</t>
+        </is>
+      </c>
+      <c r="N1479" s="10" t="inlineStr">
+        <is>
+          <t>Pago de S/50 en efectivo hecho POR FUERA de la mesa, directo a la secretaria (declarado por la directiva el 01/08/2026). No aparece en mesas, yape, blancos ni en el pool de exceso — buscado el 03/08 contra los ciclos congelados de 7_cierre/archivo/. Es plata real de la JASS que nunca entro al registro: por eso ABONO_REZAGADO (suma a caja) y no DECLARACION.</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" s="5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B1480" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C1480" s="6" t="inlineStr">
@@ -82581,7 +82611,7 @@
       <c r="F1480" s="8" t="n"/>
       <c r="G1480" s="8" t="n"/>
       <c r="H1480" s="7" t="n">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="I1480" s="7" t="n">
         <v>0</v>
@@ -82593,12 +82623,12 @@
       </c>
       <c r="K1480" s="10" t="inlineStr">
         <is>
-          <t>reclamos_2026-08-01|J-1-MULTA</t>
+          <t>notas_2026-07|C-21-MULTA-condonacion-institucional-20260809</t>
         </is>
       </c>
       <c r="L1480" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03 12:05:47</t>
+          <t>2026-08-09 09:58:37</t>
         </is>
       </c>
       <c r="M1480" s="9" t="inlineStr">
@@ -82608,7 +82638,7 @@
       </c>
       <c r="N1480" s="10" t="inlineStr">
         <is>
-          <t>exonerado por la directiva 01/08/2026 — multa faena y reunion (Comedor Popular Club de Madres)</t>
+          <t>Condonacion institucional, no es plata real. C-21 (Puesto de Salud Tupac Amaru) y J-6 (Capilla del Pueblo) figuran EXONERADO en registro_cortes.xlsx desde 2026-02: son bienes del pueblo sin vecino que participe, no generan MULTA/ACUERDOS reales. Reemplaza la cadena de 4 eventos previa (PAGO CLASE=DECLARACION_SECRETARIA del 30/07 + 3 AJUSTE de correcciones sucesivas, incluida la mia del 09/08) que quedo mal modelada: usaba el mecanismo de 'la secretaria declaro que el vecino ya pago' -- que arrastra un pendiente de investigar si es EXCESO o ABONO_REZAGADO -- para algo que nunca fue un pago, es una exencion permanente. Los 12 eventos viejos se borraron (backup: seguimiento_pueblo_pre_condonacion_institucional_C21_J6_20260809_095814.xlsx), este AJUSTE unico los reemplaza. Verificado: C-21 y J-6 no aparecen en ningun archivo precursor (abonos_rezagados.xlsx, ajustes_cargo.xlsx, genesis_tardia.xlsx, reasignaciones_aplicacion.xlsx, blancos_efectivo.xlsx) -- nada que sacar de ahi.</t>
         </is>
       </c>
     </row>
@@ -82620,12 +82650,12 @@
       </c>
       <c r="B1481" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C1481" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1481" s="6" t="inlineStr">
@@ -82641,7 +82671,7 @@
       <c r="F1481" s="8" t="n"/>
       <c r="G1481" s="8" t="n"/>
       <c r="H1481" s="7" t="n">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I1481" s="7" t="n">
         <v>0</v>
@@ -82653,12 +82683,12 @@
       </c>
       <c r="K1481" s="10" t="inlineStr">
         <is>
-          <t>reclamos_2026-08-01|J-1-ACUERDOS</t>
+          <t>notas_2026-07|J-6-MULTA-condonacion-institucional-20260809</t>
         </is>
       </c>
       <c r="L1481" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03 12:05:49</t>
+          <t>2026-08-09 09:58:39</t>
         </is>
       </c>
       <c r="M1481" s="9" t="inlineStr">
@@ -82668,24 +82698,24 @@
       </c>
       <c r="N1481" s="10" t="inlineStr">
         <is>
-          <t>exonerado por la directiva 01/08/2026 — techado y campo (Comedor Popular Club de Madres)</t>
+          <t>Condonacion institucional, no es plata real. C-21 (Puesto de Salud Tupac Amaru) y J-6 (Capilla del Pueblo) figuran EXONERADO en registro_cortes.xlsx desde 2026-02: son bienes del pueblo sin vecino que participe, no generan MULTA/ACUERDOS reales. Reemplaza la cadena de 4 eventos previa (PAGO CLASE=DECLARACION_SECRETARIA del 30/07 + 3 AJUSTE de correcciones sucesivas, incluida la mia del 09/08) que quedo mal modelada: usaba el mecanismo de 'la secretaria declaro que el vecino ya pago' -- que arrastra un pendiente de investigar si es EXCESO o ABONO_REZAGADO -- para algo que nunca fue un pago, es una exencion permanente. Los 12 eventos viejos se borraron (backup: seguimiento_pueblo_pre_condonacion_institucional_C21_J6_20260809_095814.xlsx), este AJUSTE unico los reemplaza. Verificado: C-21 y J-6 no aparecen en ningun archivo precursor (abonos_rezagados.xlsx, ajustes_cargo.xlsx, genesis_tardia.xlsx, reasignaciones_aplicacion.xlsx, blancos_efectivo.xlsx) -- nada que sacar de ahi.</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B1482" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C1482" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1482" s="6" t="inlineStr">
@@ -82701,7 +82731,7 @@
       <c r="F1482" s="8" t="n"/>
       <c r="G1482" s="8" t="n"/>
       <c r="H1482" s="7" t="n">
-        <v>-30</v>
+        <v>-75</v>
       </c>
       <c r="I1482" s="7" t="n">
         <v>0</v>
@@ -82713,12 +82743,12 @@
       </c>
       <c r="K1482" s="10" t="inlineStr">
         <is>
-          <t>reclamos_2026-08-01|O-2-MULTA</t>
+          <t>notas_2026-07|J-6-ACUERDOS-condonacion-institucional-20260809</t>
         </is>
       </c>
       <c r="L1482" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03 12:05:52</t>
+          <t>2026-08-09 09:58:41</t>
         </is>
       </c>
       <c r="M1482" s="9" t="inlineStr">
@@ -82728,24 +82758,24 @@
       </c>
       <c r="N1482" s="10" t="inlineStr">
         <is>
-          <t>exonerado por la directiva 01/08/2026 — se exonera la multa (Carmen Ingaruca Julca)</t>
+          <t>Condonacion institucional, no es plata real. C-21 (Puesto de Salud Tupac Amaru) y J-6 (Capilla del Pueblo) figuran EXONERADO en registro_cortes.xlsx desde 2026-02: son bienes del pueblo sin vecino que participe, no generan MULTA/ACUERDOS reales. Reemplaza la cadena de 4 eventos previa (PAGO CLASE=DECLARACION_SECRETARIA del 30/07 + 3 AJUSTE de correcciones sucesivas, incluida la mia del 09/08) que quedo mal modelada: usaba el mecanismo de 'la secretaria declaro que el vecino ya pago' -- que arrastra un pendiente de investigar si es EXCESO o ABONO_REZAGADO -- para algo que nunca fue un pago, es una exencion permanente. Los 12 eventos viejos se borraron (backup: seguimiento_pueblo_pre_condonacion_institucional_C21_J6_20260809_095814.xlsx), este AJUSTE unico los reemplaza. Verificado: C-21 y J-6 no aparecen en ningun archivo precursor (abonos_rezagados.xlsx, ajustes_cargo.xlsx, genesis_tardia.xlsx, reasignaciones_aplicacion.xlsx, blancos_efectivo.xlsx) -- nada que sacar de ahi.</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" s="5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B1483" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C1483" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1483" s="6" t="inlineStr">
@@ -82755,57 +82785,57 @@
       </c>
       <c r="E1483" s="6" t="inlineStr">
         <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="F1483" s="7" t="n">
-        <v>80</v>
-      </c>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1483" s="8" t="n"/>
       <c r="G1483" s="8" t="n"/>
-      <c r="H1483" s="8" t="n"/>
+      <c r="H1483" s="7" t="n">
+        <v>-50</v>
+      </c>
       <c r="I1483" s="7" t="n">
-        <v>80</v>
+        <v>-50</v>
       </c>
       <c r="J1483" s="9" t="inlineStr">
         <is>
-          <t>genesis_tardia</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1483" s="10" t="inlineStr">
         <is>
-          <t>reclamos_2026-08-01|M-12-CONVENIO</t>
+          <t>notas_2026-07|D-16-ACUERDOS-cascada-completa-20260809</t>
         </is>
       </c>
       <c r="L1483" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03 13:51:06</t>
+          <t>2026-08-09 15:03:56</t>
         </is>
       </c>
       <c r="M1483" s="9" t="inlineStr">
         <is>
-          <t>GENESIS</t>
+          <t>CORRECCION_SISTEMA</t>
         </is>
       </c>
       <c r="N1483" s="10" t="inlineStr">
         <is>
-          <t>Cargo nuevo de convenio S/80 confirmado por la directiva el 01/08/2026 (corrige el campo: se habia sembrado en MANTENIMIENTO el 28/07). SOLO REGISTRO: el efecto lo hace el CARGO del ledger — esta fila es para el backfill del libro_mayor.</t>
+          <t>Reconciliacion completa de julio incluyendo los 2 pagos reales de Wagner Trujillo: abono rezagado S/85 (yape retenido de junio, recuperado en efectivo, MES_ANO_APLICA=2026-07 en abonos_rezagados.xlsx -- NUNCA llego a aplicarse en las corridas de julio porque ese archivo es del 03-06/08, posterior a las 3 corridas de 5_cobranza de julio) + efectivo S/34 (mesa_4, 04/07). Total real disponible S/119. Cascada P1-P5 replicada externamente (agua 19 + corte 0 + multa 0[nunca sembrada, ver ajustes_cargo.xlsx] + acuerdos 50 + convenio 50 = 119 exacto): ACUERDOS y CONVENIO quedan COMPLETAMENTE PAGADOS. Corrige mi propio ajuste anterior de hoy (AJUSTE ACUERDOS +50, 'reasignacion a convenio') que estaba mal calculado por no incluir el abono rezagado -- ese ajuste y la fila de reasignaciones_aplicacion.xlsx que lo acompanaba se borraron (backup: seguimiento_pueblo_pre_cascada_completa_D16_D1_6_L4_20260809_150214.xlsx).</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B1484" s="5" t="inlineStr">
         <is>
-          <t>14A</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C1484" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>CONVENIO</t>
         </is>
       </c>
       <c r="D1484" s="6" t="inlineStr">
@@ -82821,51 +82851,51 @@
       <c r="F1484" s="8" t="n"/>
       <c r="G1484" s="8" t="n"/>
       <c r="H1484" s="7" t="n">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="I1484" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J1484" s="9" t="inlineStr">
         <is>
-          <t>reidentificacion_cargo</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1484" s="10" t="inlineStr">
         <is>
-          <t>reidentificacion_cargo|E-14A-a-E-14B|ACUERDOS|origen</t>
+          <t>notas_2026-07|D-16-CONVENIO-cascada-completa-20260809</t>
         </is>
       </c>
       <c r="L1484" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03 16:13:52</t>
+          <t>2026-08-09 15:03:57</t>
         </is>
       </c>
       <c r="M1484" s="9" t="inlineStr">
         <is>
-          <t>REASIGNACION</t>
+          <t>CORRECCION_SISTEMA</t>
         </is>
       </c>
       <c r="N1484" s="10" t="inlineStr">
         <is>
-          <t>Cargo movido a E-14B. El cargo de techado y campo (75) de JUAN SAAVEDRA SAAVEDRA se sembro el 2026-07 sobre E-14A, lote que NO existe en padron_reconciliado. La fuente (DEUDORES Y PAGOS DEL TECHADO Y CAMPO, hoja Corregido) lo lista como E-14A; el padron lo tiene como E-14B. Consecuencia: E-14A imprimio boleta sin nombre (recibo 18083) y E-14B quedo sin cargo, lo que llevo a la directiva a pedir un cargo nuevo el 01/08 (habria duplicado los 75). Se mueve al lote real.</t>
+          <t>Reconciliacion completa de julio incluyendo los 2 pagos reales de Wagner Trujillo: abono rezagado S/85 (yape retenido de junio, recuperado en efectivo, MES_ANO_APLICA=2026-07 en abonos_rezagados.xlsx -- NUNCA llego a aplicarse en las corridas de julio porque ese archivo es del 03-06/08, posterior a las 3 corridas de 5_cobranza de julio) + efectivo S/34 (mesa_4, 04/07). Total real disponible S/119. Cascada P1-P5 replicada externamente (agua 19 + corte 0 + multa 0[nunca sembrada, ver ajustes_cargo.xlsx] + acuerdos 50 + convenio 50 = 119 exacto): ACUERDOS y CONVENIO quedan COMPLETAMENTE PAGADOS. Corrige mi propio ajuste anterior de hoy (AJUSTE ACUERDOS +50, 'reasignacion a convenio') que estaba mal calculado por no incluir el abono rezagado -- ese ajuste y la fila de reasignaciones_aplicacion.xlsx que lo acompanaba se borraron (backup: seguimiento_pueblo_pre_cascada_completa_D16_D1_6_L4_20260809_150214.xlsx).</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B1485" s="5" t="inlineStr">
         <is>
-          <t>14B</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C1485" s="6" t="inlineStr">
         <is>
-          <t>ACUERDOS</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1485" s="6" t="inlineStr">
@@ -82875,47 +82905,47 @@
       </c>
       <c r="E1485" s="6" t="inlineStr">
         <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="F1485" s="7" t="n">
-        <v>75</v>
-      </c>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1485" s="8" t="n"/>
       <c r="G1485" s="8" t="n"/>
-      <c r="H1485" s="8" t="n"/>
+      <c r="H1485" s="7" t="n">
+        <v>-1</v>
+      </c>
       <c r="I1485" s="7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J1485" s="9" t="inlineStr">
         <is>
-          <t>reidentificacion_cargo</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="K1485" s="10" t="inlineStr">
         <is>
-          <t>reidentificacion_cargo|E-14A-a-E-14B|ACUERDOS|destino</t>
+          <t>notas_2026-07|D1-6-MULTA-cascada-completa-20260809</t>
         </is>
       </c>
       <c r="L1485" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03 16:13:54</t>
+          <t>2026-08-09 15:03:58</t>
         </is>
       </c>
       <c r="M1485" s="9" t="inlineStr">
         <is>
-          <t>REASIGNACION</t>
+          <t>CORRECCION_SISTEMA</t>
         </is>
       </c>
       <c r="N1485" s="10" t="inlineStr">
         <is>
-          <t>Cargo recibido desde E-14A. El cargo de techado y campo (75) de JUAN SAAVEDRA SAAVEDRA se sembro el 2026-07 sobre E-14A, lote que NO existe en padron_reconciliado. La fuente (DEUDORES Y PAGOS DEL TECHADO Y CAMPO, hoja Corregido) lo lista como E-14A; el padron lo tiene como E-14B. Consecuencia: E-14A imprimio boleta sin nombre (recibo 18083) y E-14B quedo sin cargo, lo que llevo a la directiva a pedir un cargo nuevo el 01/08 (habria duplicado los 75). Se mueve al lote real.</t>
+          <t>Reconciliacion completa de julio incluyendo los 2 pagos reales de Wagner Trujillo: abono rezagado S/33 (yape retenido de junio, recuperado en efectivo, MES_ANO_APLICA=2026-07 -- NUNCA se aplico en las corridas de julio, el archivo es de agosto) + efectivo S/33 (mesa_4, 05/07). Total real disponible S/66. Cascada P1-P5 replicada externamente (agua 16 + corte 0 + multa 30 + acuerdos 50 = 96 de deuda; 66 pagado cubre agua completo y MULTA completo, deja 20 de los 50 de ACUERDOS -- que es exactamente lo que el ledger ya tenia acreditado). Corrige solo MULTA: quedaba en 1 por el bug de signo del 20/07 (AJUSTE -12 en vez de +12), el valor correcto es 0 (multa totalmente pagada). ACUERDOS no se toca, ya estaba en el valor correcto (30).</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B1486" s="5" t="inlineStr">
@@ -82925,7 +82955,7 @@
       </c>
       <c r="C1486" s="6" t="inlineStr">
         <is>
-          <t>MULTA</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1486" s="6" t="inlineStr">
@@ -82941,10 +82971,10 @@
       <c r="F1486" s="8" t="n"/>
       <c r="G1486" s="8" t="n"/>
       <c r="H1486" s="7" t="n">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="I1486" s="7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J1486" s="9" t="inlineStr">
         <is>
@@ -82953,39 +82983,39 @@
       </c>
       <c r="K1486" s="10" t="inlineStr">
         <is>
-          <t>reclamos_2026-08-01|G-4-MULTA-reasig</t>
+          <t>notas_2026-07|L-4-ACUERDOS-cascada-completa-20260809</t>
         </is>
       </c>
       <c r="L1486" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03 17:30:25</t>
+          <t>2026-08-09 15:03:59</t>
         </is>
       </c>
       <c r="M1486" s="9" t="inlineStr">
         <is>
-          <t>REASIGNACION</t>
+          <t>CORRECCION_SISTEMA</t>
         </is>
       </c>
       <c r="N1486" s="10" t="inlineStr">
         <is>
-          <t>La secretaria confirma (01/08/2026) que su pago de MULTA de S/25 debe contarse contra CONVENIO. Se devuelve la deuda a MULTA y se acredita a CONVENIO. No hay plata nueva: es el mismo pago cambiando de concepto.</t>
+          <t>Reconciliacion completa de julio incluyendo los 2 pagos reales de Wagner Trujillo: abono rezagado S/58 (yape retenido de junio, recuperado en efectivo, MES_ANO_APLICA=2026-07 -- NUNCA se aplico en las corridas de julio, el archivo es de agosto) + efectivo S/41 (mesa_4, 05/07). Total real disponible S/99. Cascada P1-P5 replicada externamente (agua 24 + corte 0 + multa 20 + acuerdos 75 + convenio 25 = 144 de deuda; 99 pagado cubre agua y multa completos, cubre 55 de los 75 de ACUERDOS, no llega a CONVENIO). Corrige solo ACUERDOS: quedaba en 45 (PAGO 30 del 20/07, sin el resto del reparto real), el valor correcto es 20 (75 cargo - 55 pagado). MULTA y CONVENIO no se tocan, ya estaban en el valor correcto (0 y 25).</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B1487" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C1487" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>ACUERDOS</t>
         </is>
       </c>
       <c r="D1487" s="6" t="inlineStr">
@@ -83001,10 +83031,10 @@
       <c r="F1487" s="8" t="n"/>
       <c r="G1487" s="8" t="n"/>
       <c r="H1487" s="7" t="n">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="I1487" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J1487" s="9" t="inlineStr">
         <is>
@@ -83013,39 +83043,39 @@
       </c>
       <c r="K1487" s="10" t="inlineStr">
         <is>
-          <t>reclamos_2026-08-01|G-4-CONVENIO-reasig</t>
+          <t>notas_2026-07|D-16-ACUERDOS-cascada-completa-correccion-20260809</t>
         </is>
       </c>
       <c r="L1487" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03 17:30:27</t>
+          <t>2026-08-09 15:04:23</t>
         </is>
       </c>
       <c r="M1487" s="9" t="inlineStr">
         <is>
-          <t>REASIGNACION</t>
+          <t>CORRECCION_SISTEMA</t>
         </is>
       </c>
       <c r="N1487" s="10" t="inlineStr">
         <is>
-          <t>La secretaria confirma (01/08/2026) que su pago de MULTA de S/25 debe contarse contra CONVENIO. Se devuelve la deuda a MULTA y se acredita a CONVENIO. No hay plata nueva: es el mismo pago cambiando de concepto.</t>
+          <t>Correccion de mi propio error: el AJUSTE anterior (D-16-ACUERDOS-cascada-completa-20260809, -50) se calculo sobre un saldo previo incorrecto -- borre mi ajuste de la reasignacion antes de escribir este, asi que el saldo ya habia vuelto a 0 (el bug original), no a 50 como asumi. Este +50 corrige ese error de calculo, dejando el saldo en el valor correcto: 0 (ACUERDOS completamente pagado, ver motivo de la fila anterior).</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B1488" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C1488" s="6" t="inlineStr">
         <is>
-          <t>CONVENIO</t>
+          <t>MULTA</t>
         </is>
       </c>
       <c r="D1488" s="6" t="inlineStr">
@@ -83055,14 +83085,14 @@
       </c>
       <c r="E1488" s="6" t="inlineStr">
         <is>
-          <t>AJUSTE</t>
+          <t>PAGO</t>
         </is>
       </c>
       <c r="F1488" s="8" t="n"/>
-      <c r="G1488" s="8" t="n"/>
-      <c r="H1488" s="7" t="n">
-        <v>-50</v>
-      </c>
+      <c r="G1488" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1488" s="8" t="n"/>
       <c r="I1488" s="7" t="n">
         <v>0</v>
       </c>
@@ -83073,12 +83103,12 @@
       </c>
       <c r="K1488" s="10" t="inlineStr">
         <is>
-          <t>reclamos_2026-08-01|G-4-CONVENIO-abono</t>
+          <t>notas_2026-07|T-12-MULTA-abono-rezagado-20260809</t>
         </is>
       </c>
       <c r="L1488" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03 17:30:29</t>
+          <t>2026-08-09 15:16:55</t>
         </is>
       </c>
       <c r="M1488" s="9" t="inlineStr">
@@ -83088,9 +83118,4373 @@
       </c>
       <c r="N1488" s="10" t="inlineStr">
         <is>
-          <t>Pago de S/50 en efectivo hecho POR FUERA de la mesa, directo a la secretaria (declarado por la directiva el 01/08/2026). No aparece en mesas, yape, blancos ni en el pool de exceso — buscado el 03/08 contra los ciclos congelados de 7_cierre/archivo/. Es plata real de la JASS que nunca entro al registro: por eso ABONO_REZAGADO (suma a caja) y no DECLARACION.</t>
-        </is>
-      </c>
+          <t>Abono rezagado de Wagner Trujillo (yape retenido de junio, S/155, recuperado en efectivo) con MES_ANO_APLICA=2026-07 en abonos_rezagados.xlsx -- NUNCA se aplico en las 3 corridas de julio (08/07, 20/07, 31/07) porque el archivo es del 03-06/08, posterior a esas corridas. Cascada P1-P5 replicada externamente: agua 0 + corte 0 + multa 50 + acuerdos 75 = 125 de deuda, cubierta completa por los 155 (sobran 30 sin aplicar, es agua/exceso, no vive en este ledger). MULTA y ACUERDOS quedan totalmente pagados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B1489" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1489" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1489" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E1489" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1489" s="8" t="n"/>
+      <c r="G1489" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1489" s="8" t="n"/>
+      <c r="I1489" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1489" s="9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="K1489" s="10" t="inlineStr">
+        <is>
+          <t>notas_2026-07|T-12-ACUERDOS-abono-rezagado-20260809</t>
+        </is>
+      </c>
+      <c r="L1489" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:16:56</t>
+        </is>
+      </c>
+      <c r="M1489" s="9" t="inlineStr">
+        <is>
+          <t>ABONO_REZAGADO</t>
+        </is>
+      </c>
+      <c r="N1489" s="10" t="inlineStr">
+        <is>
+          <t>Abono rezagado de Wagner Trujillo (yape retenido de junio, S/155, recuperado en efectivo) con MES_ANO_APLICA=2026-07 en abonos_rezagados.xlsx -- NUNCA se aplico en las 3 corridas de julio (08/07, 20/07, 31/07) porque el archivo es del 03-06/08, posterior a esas corridas. Cascada P1-P5 replicada externamente: agua 0 + corte 0 + multa 50 + acuerdos 75 = 125 de deuda, cubierta completa por los 155 (sobran 30 sin aplicar, es agua/exceso, no vive en este ledger). MULTA y ACUERDOS quedan totalmente pagados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1490" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1490" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1490" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E1490" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1490" s="8" t="n"/>
+      <c r="G1490" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1490" s="8" t="n"/>
+      <c r="I1490" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1490" s="9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="K1490" s="10" t="inlineStr">
+        <is>
+          <t>notas_2026-07|I-9-MULTA-abono-rezagado-20260809</t>
+        </is>
+      </c>
+      <c r="L1490" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:16:57</t>
+        </is>
+      </c>
+      <c r="M1490" s="9" t="inlineStr">
+        <is>
+          <t>ABONO_REZAGADO</t>
+        </is>
+      </c>
+      <c r="N1490" s="10" t="inlineStr">
+        <is>
+          <t>Abono rezagado de Wagner Trujillo (yape retenido de junio, S/86, recuperado en efectivo) con MES_ANO_APLICA=2026-07 en abonos_rezagados.xlsx -- NUNCA se aplico en las 3 corridas de julio, el archivo es de agosto. Cascada P1-P5 replicada externamente: agua 19 + multa 50 = 69, cubierto completo por los 86, deja 17 de los 75 de acuerdos. MULTA queda totalmente pagada; ACUERDOS pasa de 75 a 58.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1491" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1491" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1491" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E1491" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1491" s="8" t="n"/>
+      <c r="G1491" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1491" s="8" t="n"/>
+      <c r="I1491" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="J1491" s="9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="K1491" s="10" t="inlineStr">
+        <is>
+          <t>notas_2026-07|I-9-ACUERDOS-abono-rezagado-20260809</t>
+        </is>
+      </c>
+      <c r="L1491" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:16:58</t>
+        </is>
+      </c>
+      <c r="M1491" s="9" t="inlineStr">
+        <is>
+          <t>ABONO_REZAGADO</t>
+        </is>
+      </c>
+      <c r="N1491" s="10" t="inlineStr">
+        <is>
+          <t>Abono rezagado de Wagner Trujillo (yape retenido de junio, S/86, recuperado en efectivo) con MES_ANO_APLICA=2026-07 en abonos_rezagados.xlsx -- NUNCA se aplico en las 3 corridas de julio, el archivo es de agosto. Cascada P1-P5 replicada externamente: agua 19 + multa 50 = 69, cubierto completo por los 86, deja 17 de los 75 de acuerdos. MULTA queda totalmente pagada; ACUERDOS pasa de 75 a 58.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B1492" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1492" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1492" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E1492" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1492" s="8" t="n"/>
+      <c r="G1492" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1492" s="8" t="n"/>
+      <c r="I1492" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1492" s="9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="K1492" s="10" t="inlineStr">
+        <is>
+          <t>notas_2026-07|F-9-CONVENIO-abono-rezagado-20260809</t>
+        </is>
+      </c>
+      <c r="L1492" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:16:59</t>
+        </is>
+      </c>
+      <c r="M1492" s="9" t="inlineStr">
+        <is>
+          <t>ABONO_REZAGADO</t>
+        </is>
+      </c>
+      <c r="N1492" s="10" t="inlineStr">
+        <is>
+          <t>Abono rezagado de Wagner Trujillo (yape retenido de junio, S/52, recuperado en efectivo) con MES_ANO_APLICA=2026-07 en abonos_rezagados.xlsx -- NUNCA se aplico en las 3 corridas de julio, el archivo es de agosto. Cascada P1-P5 replicada externamente: agua 55 + convenio 50 (post ajuste formula abril) = 105, exacto lo que trae el abono(52)+efectivo(53)=105. CONVENIO queda totalmente pagado (antes: 25, solo el efectivo se habia acreditado).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B1493" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1493" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1493" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E1493" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1493" s="8" t="n"/>
+      <c r="G1493" s="8" t="n"/>
+      <c r="H1493" s="7" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I1493" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1493" s="9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="K1493" s="10" t="inlineStr">
+        <is>
+          <t>notas_2026-07|S-5-ACUERDOS-corte-exonerado-20260809</t>
+        </is>
+      </c>
+      <c r="L1493" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:34:07</t>
+        </is>
+      </c>
+      <c r="M1493" s="9" t="inlineStr">
+        <is>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+      <c r="N1493" s="10" t="inlineStr">
+        <is>
+          <t>S-5 salio en corte por error: el pago SI existia (Wagner Trujillo lo retuvo en su yape personal de junio, recuperado en efectivo en julio -- abonos_rezagados.xlsx S/71, MES_ANO_APLICA=2026-07). Reclamo confirmado 28/07/2026 (notas_2026-07.xlsx). El corte queda exonerado (ajustes_cargo.xlsx, registro_cortes.xlsx ESTADO=EXONERADO). Al liberar los S/40 de corte de la cascada P1-P5, el abono(71)+efectivo(74)=145 ya aplicados/disponibles alcanzan para cubrir agua(70)+multa(30, ya pagada)+acuerdos neto(45, tras el credito historico de notas_2026-07) completo: 70+30+45=145 exacto. ACUERDOS pasa de 40 a 0 (saldo hoy 40 = 75 cargo - 30 credito historico - 5 pagado 20/07; con el corte exonerado, el resto del abono cubre los 40 que faltaban).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B1494" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1494" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1494" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1494" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1494" s="8" t="n"/>
+      <c r="G1494" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1494" s="8" t="n"/>
+      <c r="I1494" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J1494" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1494" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_A_1_1786365942.256341</t>
+        </is>
+      </c>
+      <c r="L1494" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:45:43</t>
+        </is>
+      </c>
+      <c r="M1494" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1494" s="10" t="inlineStr"/>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B1495" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1495" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1495" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1495" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1495" s="8" t="n"/>
+      <c r="G1495" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1495" s="8" t="n"/>
+      <c r="I1495" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1495" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1495" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_A_8_1786365959.036622</t>
+        </is>
+      </c>
+      <c r="L1495" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:45:59</t>
+        </is>
+      </c>
+      <c r="M1495" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1495" s="10" t="inlineStr"/>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B1496" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C1496" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1496" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1496" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1496" s="8" t="n"/>
+      <c r="G1496" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="H1496" s="8" t="n"/>
+      <c r="I1496" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1496" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1496" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_B_4_1786365975.960345</t>
+        </is>
+      </c>
+      <c r="L1496" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:46:16</t>
+        </is>
+      </c>
+      <c r="M1496" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1496" s="10" t="inlineStr"/>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B1497" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1497" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1497" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1497" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1497" s="8" t="n"/>
+      <c r="G1497" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1497" s="8" t="n"/>
+      <c r="I1497" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1497" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1497" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_B_5_1786365979.074332</t>
+        </is>
+      </c>
+      <c r="L1497" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:46:20</t>
+        </is>
+      </c>
+      <c r="M1497" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1497" s="10" t="inlineStr"/>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B1498" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1498" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1498" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1498" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1498" s="8" t="n"/>
+      <c r="G1498" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1498" s="8" t="n"/>
+      <c r="I1498" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="J1498" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1498" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_B_5_1786365981.217957</t>
+        </is>
+      </c>
+      <c r="L1498" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:46:22</t>
+        </is>
+      </c>
+      <c r="M1498" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1498" s="10" t="inlineStr"/>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1499" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C1499" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1499" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1499" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1499" s="8" t="n"/>
+      <c r="G1499" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1499" s="8" t="n"/>
+      <c r="I1499" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1499" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1499" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_C_16_1786366047.441671</t>
+        </is>
+      </c>
+      <c r="L1499" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:47:28</t>
+        </is>
+      </c>
+      <c r="M1499" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1499" s="10" t="inlineStr"/>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1500" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C1500" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1500" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1500" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1500" s="8" t="n"/>
+      <c r="G1500" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1500" s="8" t="n"/>
+      <c r="I1500" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="J1500" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1500" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_C_16_1786366050.820778</t>
+        </is>
+      </c>
+      <c r="L1500" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:47:31</t>
+        </is>
+      </c>
+      <c r="M1500" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1500" s="10" t="inlineStr"/>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1501" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C1501" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1501" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1501" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1501" s="8" t="n"/>
+      <c r="G1501" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1501" s="8" t="n"/>
+      <c r="I1501" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1501" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1501" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_C_17_1786366053.046327</t>
+        </is>
+      </c>
+      <c r="L1501" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:47:34</t>
+        </is>
+      </c>
+      <c r="M1501" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1501" s="10" t="inlineStr"/>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1502" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C1502" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1502" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1502" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1502" s="8" t="n"/>
+      <c r="G1502" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1502" s="8" t="n"/>
+      <c r="I1502" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1502" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1502" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_C_20_1786366061.838557</t>
+        </is>
+      </c>
+      <c r="L1502" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:47:42</t>
+        </is>
+      </c>
+      <c r="M1502" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1502" s="10" t="inlineStr"/>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B1503" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C1503" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1503" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1503" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1503" s="8" t="n"/>
+      <c r="G1503" s="8" t="n"/>
+      <c r="H1503" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I1503" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1503" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1503" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_D_16_1786366116.908351</t>
+        </is>
+      </c>
+      <c r="L1503" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:48:37</t>
+        </is>
+      </c>
+      <c r="M1503" s="9" t="inlineStr">
+        <is>
+          <t>CORRECCION_SISTEMA</t>
+        </is>
+      </c>
+      <c r="N1503" s="10" t="inlineStr">
+        <is>
+          <t>corrección: pago recalculado a la baja en 5_cobranza — se devuelve la deuda que este pago había cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1504" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C1504" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1504" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1504" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1504" s="8" t="n"/>
+      <c r="G1504" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1504" s="8" t="n"/>
+      <c r="I1504" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1504" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1504" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_4_1786366133.514179</t>
+        </is>
+      </c>
+      <c r="L1504" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:48:54</t>
+        </is>
+      </c>
+      <c r="M1504" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1504" s="10" t="inlineStr"/>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1505" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1505" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1505" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1505" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1505" s="8" t="n"/>
+      <c r="G1505" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1505" s="8" t="n"/>
+      <c r="I1505" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1505" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1505" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_12_1786366148.33936</t>
+        </is>
+      </c>
+      <c r="L1505" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:49:09</t>
+        </is>
+      </c>
+      <c r="M1505" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1505" s="10" t="inlineStr"/>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1506" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1506" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1506" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1506" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1506" s="8" t="n"/>
+      <c r="G1506" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1506" s="8" t="n"/>
+      <c r="I1506" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1506" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1506" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_E_12_1786366150.43865</t>
+        </is>
+      </c>
+      <c r="L1506" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:49:11</t>
+        </is>
+      </c>
+      <c r="M1506" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1506" s="10" t="inlineStr"/>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1507" s="5" t="inlineStr">
+        <is>
+          <t>16A</t>
+        </is>
+      </c>
+      <c r="C1507" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1507" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1507" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1507" s="8" t="n"/>
+      <c r="G1507" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1507" s="8" t="n"/>
+      <c r="I1507" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1507" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1507" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_G_16A_1786366214.551558</t>
+        </is>
+      </c>
+      <c r="L1507" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:50:15</t>
+        </is>
+      </c>
+      <c r="M1507" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1507" s="10" t="inlineStr"/>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1508" s="5" t="inlineStr">
+        <is>
+          <t>16A</t>
+        </is>
+      </c>
+      <c r="C1508" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1508" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1508" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1508" s="8" t="n"/>
+      <c r="G1508" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1508" s="8" t="n"/>
+      <c r="I1508" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1508" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1508" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_G_16A_1786366216.747257</t>
+        </is>
+      </c>
+      <c r="L1508" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:50:17</t>
+        </is>
+      </c>
+      <c r="M1508" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1508" s="10" t="inlineStr"/>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1509" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C1509" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1509" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1509" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1509" s="8" t="n"/>
+      <c r="G1509" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1509" s="8" t="n"/>
+      <c r="I1509" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J1509" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1509" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_G_17_1786366221.237536</t>
+        </is>
+      </c>
+      <c r="L1509" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:50:22</t>
+        </is>
+      </c>
+      <c r="M1509" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1509" s="10" t="inlineStr"/>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1510" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C1510" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1510" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1510" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1510" s="8" t="n"/>
+      <c r="G1510" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1510" s="8" t="n"/>
+      <c r="I1510" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1510" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1510" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_H_17_1786366268.061903</t>
+        </is>
+      </c>
+      <c r="L1510" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:51:09</t>
+        </is>
+      </c>
+      <c r="M1510" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1510" s="10" t="inlineStr"/>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1511" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C1511" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1511" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1511" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1511" s="8" t="n"/>
+      <c r="G1511" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1511" s="8" t="n"/>
+      <c r="I1511" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1511" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1511" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_H_17_1786366270.201366</t>
+        </is>
+      </c>
+      <c r="L1511" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:51:11</t>
+        </is>
+      </c>
+      <c r="M1511" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1511" s="10" t="inlineStr"/>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1512" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C1512" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1512" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1512" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1512" s="8" t="n"/>
+      <c r="G1512" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1512" s="8" t="n"/>
+      <c r="I1512" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1512" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1512" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_H_18_1786366272.601684</t>
+        </is>
+      </c>
+      <c r="L1512" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:51:13</t>
+        </is>
+      </c>
+      <c r="M1512" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1512" s="10" t="inlineStr"/>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B1513" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1513" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1513" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1513" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1513" s="8" t="n"/>
+      <c r="G1513" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="H1513" s="8" t="n"/>
+      <c r="I1513" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="J1513" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1513" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_I_5_1786366293.862614</t>
+        </is>
+      </c>
+      <c r="L1513" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:51:35</t>
+        </is>
+      </c>
+      <c r="M1513" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1513" s="10" t="inlineStr"/>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B1514" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C1514" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1514" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1514" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1514" s="8" t="n"/>
+      <c r="G1514" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1514" s="8" t="n"/>
+      <c r="I1514" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1514" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1514" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_J_11_1786366340.826723</t>
+        </is>
+      </c>
+      <c r="L1514" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:52:21</t>
+        </is>
+      </c>
+      <c r="M1514" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1514" s="10" t="inlineStr"/>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B1515" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C1515" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1515" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1515" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1515" s="8" t="n"/>
+      <c r="G1515" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1515" s="8" t="n"/>
+      <c r="I1515" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1515" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1515" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_J_13_1786366344.302555</t>
+        </is>
+      </c>
+      <c r="L1515" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:52:25</t>
+        </is>
+      </c>
+      <c r="M1515" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1515" s="10" t="inlineStr"/>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1516" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1516" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1516" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1516" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1516" s="8" t="n"/>
+      <c r="G1516" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1516" s="8" t="n"/>
+      <c r="I1516" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1516" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1516" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_M_9_1786366417.856813</t>
+        </is>
+      </c>
+      <c r="L1516" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:53:38</t>
+        </is>
+      </c>
+      <c r="M1516" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1516" s="10" t="inlineStr"/>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1517" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1517" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1517" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1517" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1517" s="8" t="n"/>
+      <c r="G1517" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1517" s="8" t="n"/>
+      <c r="I1517" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1517" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1517" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_M_12_1786366423.621057</t>
+        </is>
+      </c>
+      <c r="L1517" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:53:44</t>
+        </is>
+      </c>
+      <c r="M1517" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1517" s="10" t="inlineStr"/>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1518" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1518" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1518" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1518" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1518" s="8" t="n"/>
+      <c r="G1518" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="H1518" s="8" t="n"/>
+      <c r="I1518" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1518" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1518" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_M_12_1786366426.64574</t>
+        </is>
+      </c>
+      <c r="L1518" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:53:47</t>
+        </is>
+      </c>
+      <c r="M1518" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1518" s="10" t="inlineStr"/>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1519" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C1519" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1519" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1519" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1519" s="8" t="n"/>
+      <c r="G1519" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1519" s="8" t="n"/>
+      <c r="I1519" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1519" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1519" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_M_22_1786366446.503318</t>
+        </is>
+      </c>
+      <c r="L1519" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:54:07</t>
+        </is>
+      </c>
+      <c r="M1519" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1519" s="10" t="inlineStr"/>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1520" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C1520" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1520" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1520" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1520" s="8" t="n"/>
+      <c r="G1520" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1520" s="8" t="n"/>
+      <c r="I1520" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1520" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1520" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_O_7_1786366470.329889</t>
+        </is>
+      </c>
+      <c r="L1520" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:54:31</t>
+        </is>
+      </c>
+      <c r="M1520" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1520" s="10" t="inlineStr"/>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1521" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C1521" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1521" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1521" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1521" s="8" t="n"/>
+      <c r="G1521" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1521" s="8" t="n"/>
+      <c r="I1521" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1521" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1521" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_O_7_1786366472.573662</t>
+        </is>
+      </c>
+      <c r="L1521" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:54:33</t>
+        </is>
+      </c>
+      <c r="M1521" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1521" s="10" t="inlineStr"/>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1522" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1522" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1522" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1522" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1522" s="8" t="n"/>
+      <c r="G1522" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1522" s="8" t="n"/>
+      <c r="I1522" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1522" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1522" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_O_8_1786366476.137908</t>
+        </is>
+      </c>
+      <c r="L1522" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:54:37</t>
+        </is>
+      </c>
+      <c r="M1522" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1522" s="10" t="inlineStr"/>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1523" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C1523" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1523" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1523" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1523" s="8" t="n"/>
+      <c r="G1523" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1523" s="8" t="n"/>
+      <c r="I1523" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1523" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1523" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_O_8_1786366478.301084</t>
+        </is>
+      </c>
+      <c r="L1523" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:54:39</t>
+        </is>
+      </c>
+      <c r="M1523" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1523" s="10" t="inlineStr"/>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B1524" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C1524" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1524" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1524" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1524" s="8" t="n"/>
+      <c r="G1524" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1524" s="8" t="n"/>
+      <c r="I1524" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J1524" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1524" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_O_15_1786366492.595425</t>
+        </is>
+      </c>
+      <c r="L1524" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:54:54</t>
+        </is>
+      </c>
+      <c r="M1524" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1524" s="10" t="inlineStr"/>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B1525" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C1525" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1525" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1525" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1525" s="8" t="n"/>
+      <c r="G1525" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="H1525" s="8" t="n"/>
+      <c r="I1525" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1525" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1525" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_P_13_1786366570.663422</t>
+        </is>
+      </c>
+      <c r="L1525" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:56:11</t>
+        </is>
+      </c>
+      <c r="M1525" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1525" s="10" t="inlineStr"/>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B1526" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C1526" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1526" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1526" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1526" s="8" t="n"/>
+      <c r="G1526" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1526" s="8" t="n"/>
+      <c r="I1526" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1526" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1526" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_P_14_1786366574.889816</t>
+        </is>
+      </c>
+      <c r="L1526" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:56:16</t>
+        </is>
+      </c>
+      <c r="M1526" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1526" s="10" t="inlineStr"/>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="5" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B1527" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C1527" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1527" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1527" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1527" s="8" t="n"/>
+      <c r="G1527" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1527" s="8" t="n"/>
+      <c r="I1527" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1527" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1527" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_Q_14_1786366610.044557</t>
+        </is>
+      </c>
+      <c r="L1527" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:56:51</t>
+        </is>
+      </c>
+      <c r="M1527" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1527" s="10" t="inlineStr"/>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B1528" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C1528" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1528" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1528" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1528" s="8" t="n"/>
+      <c r="G1528" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1528" s="8" t="n"/>
+      <c r="I1528" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1528" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1528" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_S_3_1786366641.779888</t>
+        </is>
+      </c>
+      <c r="L1528" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:57:23</t>
+        </is>
+      </c>
+      <c r="M1528" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1528" s="10" t="inlineStr"/>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1529" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C1529" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1529" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1529" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1529" s="8" t="n"/>
+      <c r="G1529" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1529" s="8" t="n"/>
+      <c r="I1529" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1529" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1529" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_W_7_1786366771.617</t>
+        </is>
+      </c>
+      <c r="L1529" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 07:59:32</t>
+        </is>
+      </c>
+      <c r="M1529" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1529" s="10" t="inlineStr"/>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B1530" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C1530" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1530" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1530" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1530" s="8" t="n"/>
+      <c r="G1530" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1530" s="8" t="n"/>
+      <c r="I1530" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1530" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1530" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_X_32_1786366825.164101</t>
+        </is>
+      </c>
+      <c r="L1530" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:00:26</t>
+        </is>
+      </c>
+      <c r="M1530" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1530" s="10" t="inlineStr"/>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="5" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B1531" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C1531" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1531" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1531" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1531" s="8" t="n"/>
+      <c r="G1531" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1531" s="8" t="n"/>
+      <c r="I1531" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1531" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1531" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_Z_7_1786366863.826065</t>
+        </is>
+      </c>
+      <c r="L1531" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:01:04</t>
+        </is>
+      </c>
+      <c r="M1531" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1531" s="10" t="inlineStr"/>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="5" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B1532" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1532" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1532" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1532" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1532" s="8" t="n"/>
+      <c r="G1532" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1532" s="8" t="n"/>
+      <c r="I1532" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1532" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1532" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_Z_12_1786366875.577575</t>
+        </is>
+      </c>
+      <c r="L1532" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:01:17</t>
+        </is>
+      </c>
+      <c r="M1532" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1532" s="10" t="inlineStr"/>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="5" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B1533" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C1533" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1533" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1533" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1533" s="8" t="n"/>
+      <c r="G1533" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1533" s="8" t="n"/>
+      <c r="I1533" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1533" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1533" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_Z_15_1786366892.928337</t>
+        </is>
+      </c>
+      <c r="L1533" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:01:34</t>
+        </is>
+      </c>
+      <c r="M1533" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1533" s="10" t="inlineStr"/>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="5" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B1534" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C1534" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1534" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1534" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1534" s="8" t="n"/>
+      <c r="G1534" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1534" s="8" t="n"/>
+      <c r="I1534" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1534" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1534" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_A1_11_1786366929.780924</t>
+        </is>
+      </c>
+      <c r="L1534" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:02:11</t>
+        </is>
+      </c>
+      <c r="M1534" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1534" s="10" t="inlineStr"/>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B1535" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1535" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1535" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1535" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1535" s="8" t="n"/>
+      <c r="G1535" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1535" s="8" t="n"/>
+      <c r="I1535" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1535" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1535" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_B1_5_1786366949.013415</t>
+        </is>
+      </c>
+      <c r="L1535" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:02:31</t>
+        </is>
+      </c>
+      <c r="M1535" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1535" s="10" t="inlineStr"/>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B1536" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C1536" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1536" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1536" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1536" s="8" t="n"/>
+      <c r="G1536" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1536" s="8" t="n"/>
+      <c r="I1536" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1536" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1536" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_B1_13_1786366970.361451</t>
+        </is>
+      </c>
+      <c r="L1536" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:02:51</t>
+        </is>
+      </c>
+      <c r="M1536" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1536" s="10" t="inlineStr"/>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B1537" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C1537" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1537" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1537" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1537" s="8" t="n"/>
+      <c r="G1537" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1537" s="8" t="n"/>
+      <c r="I1537" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1537" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1537" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_B1_13_1786366973.20289</t>
+        </is>
+      </c>
+      <c r="L1537" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:02:54</t>
+        </is>
+      </c>
+      <c r="M1537" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1537" s="10" t="inlineStr"/>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B1538" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C1538" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1538" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1538" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1538" s="8" t="n"/>
+      <c r="G1538" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1538" s="8" t="n"/>
+      <c r="I1538" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1538" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1538" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_B1_14_1786366976.568997</t>
+        </is>
+      </c>
+      <c r="L1538" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:02:57</t>
+        </is>
+      </c>
+      <c r="M1538" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1538" s="10" t="inlineStr"/>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B1539" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C1539" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1539" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1539" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1539" s="8" t="n"/>
+      <c r="G1539" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1539" s="8" t="n"/>
+      <c r="I1539" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J1539" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1539" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_C1_3_1786366985.626142</t>
+        </is>
+      </c>
+      <c r="L1539" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:03:06</t>
+        </is>
+      </c>
+      <c r="M1539" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1539" s="10" t="inlineStr"/>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B1540" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C1540" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1540" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1540" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1540" s="8" t="n"/>
+      <c r="G1540" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="H1540" s="8" t="n"/>
+      <c r="I1540" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1540" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1540" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_C1_14_1786367005.148682</t>
+        </is>
+      </c>
+      <c r="L1540" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:03:26</t>
+        </is>
+      </c>
+      <c r="M1540" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1540" s="10" t="inlineStr"/>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B1541" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C1541" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1541" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1541" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1541" s="8" t="n"/>
+      <c r="G1541" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1541" s="8" t="n"/>
+      <c r="I1541" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J1541" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1541" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_D1_6_1786367023.563793</t>
+        </is>
+      </c>
+      <c r="L1541" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:03:44</t>
+        </is>
+      </c>
+      <c r="M1541" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1541" s="10" t="inlineStr"/>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B1542" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C1542" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1542" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1542" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1542" s="8" t="n"/>
+      <c r="G1542" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1542" s="8" t="n"/>
+      <c r="I1542" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1542" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1542" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_D1_6_1786367025.943053</t>
+        </is>
+      </c>
+      <c r="L1542" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:03:46</t>
+        </is>
+      </c>
+      <c r="M1542" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1542" s="10" t="inlineStr"/>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="5" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B1543" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C1543" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1543" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1543" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1543" s="8" t="n"/>
+      <c r="G1543" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="H1543" s="8" t="n"/>
+      <c r="I1543" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="J1543" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1543" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_F1_13_1786367062.431693</t>
+        </is>
+      </c>
+      <c r="L1543" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:04:23</t>
+        </is>
+      </c>
+      <c r="M1543" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1543" s="10" t="inlineStr"/>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B1544" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C1544" s="6" t="inlineStr">
+        <is>
+          <t>CONVENIO</t>
+        </is>
+      </c>
+      <c r="D1544" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1544" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1544" s="8" t="n"/>
+      <c r="G1544" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1544" s="8" t="n"/>
+      <c r="I1544" s="7" t="n">
+        <v>1050</v>
+      </c>
+      <c r="J1544" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1544" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_CONVENIO_H1_2_1786367081.182568</t>
+        </is>
+      </c>
+      <c r="L1544" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:04:42</t>
+        </is>
+      </c>
+      <c r="M1544" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1544" s="10" t="inlineStr"/>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B1545" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C1545" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1545" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1545" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1545" s="8" t="n"/>
+      <c r="G1545" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1545" s="8" t="n"/>
+      <c r="I1545" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1545" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1545" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_H1_12_1786367098.28486</t>
+        </is>
+      </c>
+      <c r="L1545" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:04:59</t>
+        </is>
+      </c>
+      <c r="M1545" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1545" s="10" t="inlineStr"/>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B1546" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C1546" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1546" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1546" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1546" s="8" t="n"/>
+      <c r="G1546" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1546" s="8" t="n"/>
+      <c r="I1546" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="J1546" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1546" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_H1_15_1786367103.936469</t>
+        </is>
+      </c>
+      <c r="L1546" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:05:04</t>
+        </is>
+      </c>
+      <c r="M1546" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1546" s="10" t="inlineStr"/>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B1547" s="5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C1547" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1547" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1547" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1547" s="8" t="n"/>
+      <c r="G1547" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1547" s="8" t="n"/>
+      <c r="I1547" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J1547" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1547" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_H1_35_1786367109.708529</t>
+        </is>
+      </c>
+      <c r="L1547" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:05:10</t>
+        </is>
+      </c>
+      <c r="M1547" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1547" s="10" t="inlineStr"/>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1548" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1548" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1548" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1548" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1548" s="8" t="n"/>
+      <c r="G1548" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1548" s="8" t="n"/>
+      <c r="I1548" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1548" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1548" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786367145.813791</t>
+        </is>
+      </c>
+      <c r="L1548" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:05:46</t>
+        </is>
+      </c>
+      <c r="M1548" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1548" s="10" t="inlineStr"/>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B1549" s="5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C1549" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1549" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1549" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1549" s="8" t="n"/>
+      <c r="G1549" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1549" s="8" t="n"/>
+      <c r="I1549" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="J1549" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1549" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_C_36_1786370226.440435</t>
+        </is>
+      </c>
+      <c r="L1549" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:57:08</t>
+        </is>
+      </c>
+      <c r="M1549" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1549" s="10" t="inlineStr"/>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1550" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1550" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1550" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1550" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1550" s="8" t="n"/>
+      <c r="G1550" s="8" t="n"/>
+      <c r="H1550" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1550" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1550" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1550" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786370355.864173</t>
+        </is>
+      </c>
+      <c r="L1550" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:59:17</t>
+        </is>
+      </c>
+      <c r="M1550" s="9" t="inlineStr">
+        <is>
+          <t>CORRECCION_SISTEMA</t>
+        </is>
+      </c>
+      <c r="N1550" s="10" t="inlineStr">
+        <is>
+          <t>corrección: pago recalculado a la baja en 5_cobranza — se devuelve la deuda que este pago había cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1551" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1551" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1551" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1551" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1551" s="8" t="n"/>
+      <c r="G1551" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1551" s="8" t="n"/>
+      <c r="I1551" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1551" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1551" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786371881.576147</t>
+        </is>
+      </c>
+      <c r="L1551" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:24:42</t>
+        </is>
+      </c>
+      <c r="M1551" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1551" s="10" t="inlineStr"/>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1552" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1552" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1552" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1552" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1552" s="8" t="n"/>
+      <c r="G1552" s="8" t="n"/>
+      <c r="H1552" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1552" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1552" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1552" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786372263.008827</t>
+        </is>
+      </c>
+      <c r="L1552" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:31:03</t>
+        </is>
+      </c>
+      <c r="M1552" s="9" t="inlineStr">
+        <is>
+          <t>CORRECCION_SISTEMA</t>
+        </is>
+      </c>
+      <c r="N1552" s="10" t="inlineStr">
+        <is>
+          <t>corrección: pago recalculado a la baja en 5_cobranza — se devuelve la deuda que este pago había cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1553" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1553" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1553" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1553" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1553" s="8" t="n"/>
+      <c r="G1553" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1553" s="8" t="n"/>
+      <c r="I1553" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1553" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1553" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786372917.657134</t>
+        </is>
+      </c>
+      <c r="L1553" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:41:58</t>
+        </is>
+      </c>
+      <c r="M1553" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1553" s="10" t="inlineStr"/>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1554" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1554" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1554" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1554" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1554" s="8" t="n"/>
+      <c r="G1554" s="8" t="n"/>
+      <c r="H1554" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1554" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1554" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1554" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786381560.963779</t>
+        </is>
+      </c>
+      <c r="L1554" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:06:01</t>
+        </is>
+      </c>
+      <c r="M1554" s="9" t="inlineStr">
+        <is>
+          <t>CORRECCION_SISTEMA</t>
+        </is>
+      </c>
+      <c r="N1554" s="10" t="inlineStr">
+        <is>
+          <t>corrección: pago recalculado a la baja en 5_cobranza — se devuelve la deuda que este pago había cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1555" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1555" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1555" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1555" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1555" s="8" t="n"/>
+      <c r="G1555" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1555" s="8" t="n"/>
+      <c r="I1555" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1555" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1555" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786382242.011207</t>
+        </is>
+      </c>
+      <c r="L1555" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:17:22</t>
+        </is>
+      </c>
+      <c r="M1555" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1555" s="10" t="inlineStr"/>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1556" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1556" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1556" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1556" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1556" s="8" t="n"/>
+      <c r="G1556" s="8" t="n"/>
+      <c r="H1556" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1556" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1556" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1556" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786388560.794183</t>
+        </is>
+      </c>
+      <c r="L1556" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:02:41</t>
+        </is>
+      </c>
+      <c r="M1556" s="9" t="inlineStr">
+        <is>
+          <t>CORRECCION_SISTEMA</t>
+        </is>
+      </c>
+      <c r="N1556" s="10" t="inlineStr">
+        <is>
+          <t>corrección: pago recalculado a la baja en 5_cobranza — se devuelve la deuda que este pago había cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1557" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1557" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1557" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1557" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1557" s="8" t="n"/>
+      <c r="G1557" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1557" s="8" t="n"/>
+      <c r="I1557" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1557" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1557" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786389230.87644</t>
+        </is>
+      </c>
+      <c r="L1557" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:13:51</t>
+        </is>
+      </c>
+      <c r="M1557" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1557" s="10" t="inlineStr"/>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1558" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1558" s="6" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="D1558" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1558" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1558" s="8" t="n"/>
+      <c r="G1558" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1558" s="8" t="n"/>
+      <c r="I1558" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1558" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1558" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_MULTA_L_9_1786389266.005532</t>
+        </is>
+      </c>
+      <c r="L1558" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:14:26</t>
+        </is>
+      </c>
+      <c r="M1558" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1558" s="10" t="inlineStr"/>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B1559" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C1559" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1559" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1559" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1559" s="8" t="n"/>
+      <c r="G1559" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1559" s="8" t="n"/>
+      <c r="I1559" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1559" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1559" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_L_9_1786389268.024194</t>
+        </is>
+      </c>
+      <c r="L1559" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:14:28</t>
+        </is>
+      </c>
+      <c r="M1559" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1559" s="10" t="inlineStr"/>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1560" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1560" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1560" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1560" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1560" s="8" t="n"/>
+      <c r="G1560" s="8" t="n"/>
+      <c r="H1560" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1560" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1560" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1560" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786394939.487525</t>
+        </is>
+      </c>
+      <c r="L1560" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:49:00</t>
+        </is>
+      </c>
+      <c r="M1560" s="9" t="inlineStr">
+        <is>
+          <t>CORRECCION_SISTEMA</t>
+        </is>
+      </c>
+      <c r="N1560" s="10" t="inlineStr">
+        <is>
+          <t>corrección: pago recalculado a la baja en 5_cobranza — se devuelve la deuda que este pago había cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1561" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1561" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1561" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1561" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1561" s="8" t="n"/>
+      <c r="G1561" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1561" s="8" t="n"/>
+      <c r="I1561" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1561" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1561" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786395618.582013</t>
+        </is>
+      </c>
+      <c r="L1561" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:00:19</t>
+        </is>
+      </c>
+      <c r="M1561" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1561" s="10" t="inlineStr"/>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1562" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1562" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1562" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1562" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1562" s="8" t="n"/>
+      <c r="G1562" s="8" t="n"/>
+      <c r="H1562" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1562" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1562" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1562" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786403663.149974</t>
+        </is>
+      </c>
+      <c r="L1562" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:14:24</t>
+        </is>
+      </c>
+      <c r="M1562" s="9" t="inlineStr">
+        <is>
+          <t>CORRECCION_SISTEMA</t>
+        </is>
+      </c>
+      <c r="N1562" s="10" t="inlineStr">
+        <is>
+          <t>corrección: pago recalculado a la baja en 5_cobranza — se devuelve la deuda que este pago había cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1563" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1563" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1563" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1563" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1563" s="8" t="n"/>
+      <c r="G1563" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1563" s="8" t="n"/>
+      <c r="I1563" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1563" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1563" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786405644.601103</t>
+        </is>
+      </c>
+      <c r="L1563" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:47:25</t>
+        </is>
+      </c>
+      <c r="M1563" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1563" s="10" t="inlineStr"/>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1564" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1564" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1564" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1564" s="6" t="inlineStr">
+        <is>
+          <t>AJUSTE</t>
+        </is>
+      </c>
+      <c r="F1564" s="8" t="n"/>
+      <c r="G1564" s="8" t="n"/>
+      <c r="H1564" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1564" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1564" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1564" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786407215.52608</t>
+        </is>
+      </c>
+      <c r="L1564" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:13:36</t>
+        </is>
+      </c>
+      <c r="M1564" s="9" t="inlineStr">
+        <is>
+          <t>CORRECCION_SISTEMA</t>
+        </is>
+      </c>
+      <c r="N1564" s="10" t="inlineStr">
+        <is>
+          <t>corrección: pago recalculado a la baja en 5_cobranza — se devuelve la deuda que este pago había cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B1565" s="5" t="inlineStr">
+        <is>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="C1565" s="6" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="D1565" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E1565" s="6" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+      <c r="F1565" s="8" t="n"/>
+      <c r="G1565" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1565" s="8" t="n"/>
+      <c r="I1565" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1565" s="9" t="inlineStr">
+        <is>
+          <t>5_cobranza</t>
+        </is>
+      </c>
+      <c r="K1565" s="10" t="inlineStr">
+        <is>
+          <t>recon_2026-08_ACUERDOS_E_14B_1786411042.632829</t>
+        </is>
+      </c>
+      <c r="L1565" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10 20:17:23</t>
+        </is>
+      </c>
+      <c r="M1565" s="9" t="inlineStr">
+        <is>
+          <t>COBRANZA</t>
+        </is>
+      </c>
+      <c r="N1565" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
